--- a/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_ADJR2.xlsx
@@ -19,9 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV0_ADJR2</t>
   </si>
   <si>
     <t>LV1_ADJR2</t>
@@ -211,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +226,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,54 +251,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -602,15 +560,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -659,2310 +618,2451 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>0.39949807661031861</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C2">
-        <v>0.5778887398808924</v>
+        <v>0.39815189499627168</v>
       </c>
       <c r="D2">
-        <v>0.61173451812214086</v>
+        <v>0.57787455393980247</v>
       </c>
       <c r="E2">
-        <v>0.62396087613724505</v>
+        <v>0.61176472064984433</v>
       </c>
       <c r="F2">
-        <v>0.60865282795854192</v>
+        <v>0.62463140683688834</v>
       </c>
       <c r="G2">
-        <v>0.63479168559775567</v>
+        <v>0.6111233904392831</v>
       </c>
       <c r="H2">
-        <v>0.63937132330552249</v>
+        <v>0.6359304564778907</v>
       </c>
       <c r="I2">
-        <v>0.61456526948119161</v>
+        <v>0.64149044279366652</v>
       </c>
       <c r="J2">
-        <v>0.63081707898193529</v>
+        <v>0.61841269666002674</v>
       </c>
       <c r="K2">
-        <v>0.61250360281830962</v>
+        <v>0.63320109248164513</v>
       </c>
       <c r="L2">
-        <v>0.60046446436386536</v>
+        <v>0.6147839562587486</v>
       </c>
       <c r="M2">
-        <v>0.55438877317775015</v>
+        <v>0.60253043810342277</v>
       </c>
       <c r="N2">
-        <v>0.49568230464910051</v>
+        <v>0.56194516669014827</v>
       </c>
       <c r="O2">
-        <v>0.44422671331196911</v>
+        <v>0.49893119971929739</v>
       </c>
       <c r="P2">
-        <v>0.41413257905961193</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.45075554028388648</v>
+      </c>
+      <c r="Q2">
+        <v>0.42095131686386272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>0.46010448333741671</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C3">
-        <v>0.59615066145321649</v>
+        <v>0.4620080546524713</v>
       </c>
       <c r="D3">
-        <v>0.58454504983253508</v>
+        <v>0.5955512898292521</v>
       </c>
       <c r="E3">
-        <v>0.54234893909964355</v>
+        <v>0.58341388428132868</v>
       </c>
       <c r="F3">
-        <v>0.56791262235582285</v>
+        <v>0.54340105501470759</v>
       </c>
       <c r="G3">
-        <v>0.57164349928695091</v>
+        <v>0.57275739904981848</v>
       </c>
       <c r="H3">
-        <v>0.52544792544667007</v>
+        <v>0.57583367625568382</v>
       </c>
       <c r="I3">
-        <v>0.51331224790009844</v>
+        <v>0.52723528631210392</v>
       </c>
       <c r="J3">
-        <v>0.46867670351406332</v>
+        <v>0.51427893723594487</v>
       </c>
       <c r="K3">
-        <v>0.4510062798428508</v>
+        <v>0.46599067167480102</v>
       </c>
       <c r="L3">
-        <v>0.42748948879644189</v>
+        <v>0.4455050363247377</v>
       </c>
       <c r="M3">
-        <v>0.38482728009759581</v>
+        <v>0.4212638893461268</v>
       </c>
       <c r="N3">
-        <v>0.35577711358155029</v>
+        <v>0.37706437297776502</v>
       </c>
       <c r="O3">
-        <v>0.35352135607803509</v>
+        <v>0.34274170001672177</v>
       </c>
       <c r="P3">
-        <v>0.36758739691629039</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.34229048093532888</v>
+      </c>
+      <c r="Q3">
+        <v>0.35805029830346269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>0.4200441387926489</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C4">
-        <v>0.56658236486920577</v>
+        <v>0.42094741306103189</v>
       </c>
       <c r="D4">
-        <v>0.57523736768543055</v>
+        <v>0.5671615771206836</v>
       </c>
       <c r="E4">
-        <v>0.58782216624095329</v>
+        <v>0.57602670353349517</v>
       </c>
       <c r="F4">
-        <v>0.59699637609327783</v>
+        <v>0.58676545092628518</v>
       </c>
       <c r="G4">
-        <v>0.6366304212236259</v>
+        <v>0.59511389560741457</v>
       </c>
       <c r="H4">
-        <v>0.63861531743220379</v>
+        <v>0.63641865726913838</v>
       </c>
       <c r="I4">
-        <v>0.62822192976545332</v>
+        <v>0.63885407739461486</v>
       </c>
       <c r="J4">
-        <v>0.60505896809031179</v>
+        <v>0.62680484220873278</v>
       </c>
       <c r="K4">
-        <v>0.58473496288991422</v>
+        <v>0.60679232006620376</v>
       </c>
       <c r="L4">
-        <v>0.54971234923296652</v>
+        <v>0.57650683501590083</v>
       </c>
       <c r="M4">
-        <v>0.49781683364282081</v>
+        <v>0.54353857515041204</v>
       </c>
       <c r="N4">
-        <v>0.44461167694731191</v>
+        <v>0.48617071797042138</v>
       </c>
       <c r="O4">
-        <v>0.40954988409495308</v>
+        <v>0.43496642624865289</v>
       </c>
       <c r="P4">
-        <v>0.37675625690255998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.39869383938894309</v>
+      </c>
+      <c r="Q4">
+        <v>0.36880905378071732</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>0.58727574320870835</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C5">
-        <v>0.59437749505478032</v>
+        <v>0.58848210272375623</v>
       </c>
       <c r="D5">
-        <v>0.60266564985083382</v>
+        <v>0.59537719904355635</v>
       </c>
       <c r="E5">
-        <v>0.59776812294997317</v>
+        <v>0.60260907327611279</v>
       </c>
       <c r="F5">
-        <v>0.60565329089112996</v>
+        <v>0.59693460208020732</v>
       </c>
       <c r="G5">
-        <v>0.6057870473757867</v>
+        <v>0.60447150262537352</v>
       </c>
       <c r="H5">
-        <v>0.58748259667491065</v>
+        <v>0.60265773515026766</v>
       </c>
       <c r="I5">
-        <v>0.54748414223419206</v>
+        <v>0.58572709370297815</v>
       </c>
       <c r="J5">
-        <v>0.47257339335949772</v>
+        <v>0.54555270874502837</v>
       </c>
       <c r="K5">
-        <v>0.43169524824191252</v>
+        <v>0.47163604316932622</v>
       </c>
       <c r="L5">
-        <v>0.40448534596573898</v>
+        <v>0.4329583363011611</v>
       </c>
       <c r="M5">
-        <v>0.39657854448669261</v>
+        <v>0.40130554676409957</v>
       </c>
       <c r="N5">
-        <v>0.40556822103701312</v>
+        <v>0.39923194943718882</v>
       </c>
       <c r="O5">
-        <v>0.40453608627242388</v>
+        <v>0.40524570420345241</v>
       </c>
       <c r="P5">
-        <v>0.39714980367618302</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.40387401333989098</v>
+      </c>
+      <c r="Q5">
+        <v>0.39808635137944542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>0.58570200585998833</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C6">
-        <v>0.59271043680324254</v>
+        <v>0.58700105037331329</v>
       </c>
       <c r="D6">
-        <v>0.60433622932633602</v>
+        <v>0.5939857513291249</v>
       </c>
       <c r="E6">
-        <v>0.60745196416029423</v>
+        <v>0.6051034332421813</v>
       </c>
       <c r="F6">
-        <v>0.6292631189634954</v>
+        <v>0.61031416994237764</v>
       </c>
       <c r="G6">
-        <v>0.62076229807234717</v>
+        <v>0.6309672218931901</v>
       </c>
       <c r="H6">
-        <v>0.59196950758590006</v>
+        <v>0.62353375694852531</v>
       </c>
       <c r="I6">
-        <v>0.5686656052258614</v>
+        <v>0.59759302988529706</v>
       </c>
       <c r="J6">
-        <v>0.53347859333208025</v>
+        <v>0.57248611455445464</v>
       </c>
       <c r="K6">
-        <v>0.51829141956989311</v>
+        <v>0.53929703663291828</v>
       </c>
       <c r="L6">
-        <v>0.48746453834566628</v>
+        <v>0.52358917515587033</v>
       </c>
       <c r="M6">
-        <v>0.46517881218131818</v>
+        <v>0.49427514047767113</v>
       </c>
       <c r="N6">
-        <v>0.4495143713817592</v>
+        <v>0.47590498622381128</v>
       </c>
       <c r="O6">
-        <v>0.44400908096564218</v>
+        <v>0.45376615529974929</v>
       </c>
       <c r="P6">
-        <v>0.43330573725395422</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.44747193975219729</v>
+      </c>
+      <c r="Q6">
+        <v>0.43930241553975152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>0.42424586926041258</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C7">
-        <v>0.57857116949879317</v>
+        <v>0.42690265688449891</v>
       </c>
       <c r="D7">
-        <v>0.6264401823427499</v>
+        <v>0.5813186378298314</v>
       </c>
       <c r="E7">
-        <v>0.63601688921137878</v>
+        <v>0.63021196348481923</v>
       </c>
       <c r="F7">
-        <v>0.63422906786207511</v>
+        <v>0.63922997146562954</v>
       </c>
       <c r="G7">
-        <v>0.64495846523863043</v>
+        <v>0.63780505740827587</v>
       </c>
       <c r="H7">
-        <v>0.63326654244873437</v>
+        <v>0.64876984802161475</v>
       </c>
       <c r="I7">
-        <v>0.63344297869389343</v>
+        <v>0.63370293920201071</v>
       </c>
       <c r="J7">
-        <v>0.6203047005024146</v>
+        <v>0.63512334494500311</v>
       </c>
       <c r="K7">
-        <v>0.59240824150440674</v>
+        <v>0.62371305045799985</v>
       </c>
       <c r="L7">
-        <v>0.56673105941978097</v>
+        <v>0.5977849326005068</v>
       </c>
       <c r="M7">
-        <v>0.50143297036935419</v>
+        <v>0.56988072249955513</v>
       </c>
       <c r="N7">
-        <v>0.45806865776688571</v>
+        <v>0.50479567082936372</v>
       </c>
       <c r="O7">
-        <v>0.40502679722394641</v>
+        <v>0.46175203592725661</v>
       </c>
       <c r="P7">
-        <v>0.3713780396245025</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.4139031763988601</v>
+      </c>
+      <c r="Q7">
+        <v>0.37751469823517447</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>0.49894465560567508</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C8">
-        <v>0.57628446999183536</v>
+        <v>0.49953262606958287</v>
       </c>
       <c r="D8">
-        <v>0.62760088392921676</v>
+        <v>0.57600903686765126</v>
       </c>
       <c r="E8">
-        <v>0.64232003257022563</v>
+        <v>0.62732854345088462</v>
       </c>
       <c r="F8">
-        <v>0.64651522444801268</v>
+        <v>0.64039357418131304</v>
       </c>
       <c r="G8">
-        <v>0.63227529762751922</v>
+        <v>0.64686235120286417</v>
       </c>
       <c r="H8">
-        <v>0.63227836628116107</v>
+        <v>0.63651765860438558</v>
       </c>
       <c r="I8">
-        <v>0.60839377115588367</v>
+        <v>0.63447392962171201</v>
       </c>
       <c r="J8">
-        <v>0.56596412437698418</v>
+        <v>0.60734448034278232</v>
       </c>
       <c r="K8">
-        <v>0.54758074868032514</v>
+        <v>0.56546192398174588</v>
       </c>
       <c r="L8">
-        <v>0.5271127569952504</v>
+        <v>0.54320336430408711</v>
       </c>
       <c r="M8">
-        <v>0.48898022306530547</v>
+        <v>0.52180283819461615</v>
       </c>
       <c r="N8">
-        <v>0.42242409498602468</v>
+        <v>0.48625369832544191</v>
       </c>
       <c r="O8">
-        <v>0.37043261331272359</v>
+        <v>0.42036149027107422</v>
       </c>
       <c r="P8">
-        <v>0.33900022687513531</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.37164421021123212</v>
+      </c>
+      <c r="Q8">
+        <v>0.33808195211895681</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>0.50072693780835142</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C9">
-        <v>0.5774389581843502</v>
+        <v>0.49938038624550168</v>
       </c>
       <c r="D9">
-        <v>0.62865745998321165</v>
+        <v>0.57649620843067273</v>
       </c>
       <c r="E9">
-        <v>0.64225947746920875</v>
+        <v>0.62667936242333311</v>
       </c>
       <c r="F9">
-        <v>0.65111457715963383</v>
+        <v>0.63981319155476424</v>
       </c>
       <c r="G9">
-        <v>0.64198781012187767</v>
+        <v>0.64769707440644864</v>
       </c>
       <c r="H9">
-        <v>0.64496107071692577</v>
+        <v>0.63630950433631683</v>
       </c>
       <c r="I9">
-        <v>0.63761354179744911</v>
+        <v>0.63829929034859001</v>
       </c>
       <c r="J9">
-        <v>0.61854456521919798</v>
+        <v>0.63086184330794837</v>
       </c>
       <c r="K9">
-        <v>0.60480084613811347</v>
+        <v>0.60962110079977394</v>
       </c>
       <c r="L9">
-        <v>0.6041015143795585</v>
+        <v>0.60051910657040053</v>
       </c>
       <c r="M9">
-        <v>0.59547110410813764</v>
+        <v>0.59988667290925946</v>
       </c>
       <c r="N9">
-        <v>0.56424908830713305</v>
+        <v>0.59047245817070204</v>
       </c>
       <c r="O9">
-        <v>0.54838712195661832</v>
+        <v>0.55897035888363911</v>
       </c>
       <c r="P9">
-        <v>0.52980796112059969</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.5431045571497386</v>
+      </c>
+      <c r="Q9">
+        <v>0.52343760857770094</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>0.49810575837250898</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C10">
-        <v>0.57548615373361234</v>
+        <v>0.49990240040785289</v>
       </c>
       <c r="D10">
-        <v>0.62751471683369131</v>
+        <v>0.57726167486777236</v>
       </c>
       <c r="E10">
-        <v>0.64189935362854278</v>
+        <v>0.62794504060163814</v>
       </c>
       <c r="F10">
-        <v>0.648205662648487</v>
+        <v>0.6421462048051485</v>
       </c>
       <c r="G10">
-        <v>0.63981037845400013</v>
+        <v>0.65222971539842822</v>
       </c>
       <c r="H10">
-        <v>0.64313846383425033</v>
+        <v>0.64073812103338934</v>
       </c>
       <c r="I10">
-        <v>0.63653853263480142</v>
+        <v>0.6432897635854401</v>
       </c>
       <c r="J10">
-        <v>0.61815862908283914</v>
+        <v>0.6365296250071264</v>
       </c>
       <c r="K10">
-        <v>0.60771356549707023</v>
+        <v>0.62029159228443331</v>
       </c>
       <c r="L10">
-        <v>0.60701853343964229</v>
+        <v>0.60798901763432467</v>
       </c>
       <c r="M10">
-        <v>0.59688264949530556</v>
+        <v>0.60601912346763542</v>
       </c>
       <c r="N10">
-        <v>0.56649358215892132</v>
+        <v>0.59560051661658109</v>
       </c>
       <c r="O10">
-        <v>0.54849563522049827</v>
+        <v>0.56437210452920072</v>
       </c>
       <c r="P10">
-        <v>0.52614901748017828</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.54591199225214115</v>
+      </c>
+      <c r="Q10">
+        <v>0.52046816921103523</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>0.49911381338972433</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C11">
-        <v>0.57645841948299359</v>
+        <v>0.49861283361294267</v>
       </c>
       <c r="D11">
-        <v>0.62659883563246055</v>
+        <v>0.57536031216446815</v>
       </c>
       <c r="E11">
-        <v>0.63978993705029563</v>
+        <v>0.6271815643116212</v>
       </c>
       <c r="F11">
-        <v>0.64679678444100785</v>
+        <v>0.63971879794023256</v>
       </c>
       <c r="G11">
-        <v>0.63647158484225563</v>
+        <v>0.64739583443646354</v>
       </c>
       <c r="H11">
-        <v>0.6385162835441851</v>
+        <v>0.63800464036618421</v>
       </c>
       <c r="I11">
-        <v>0.63224164916245029</v>
+        <v>0.63834810185657098</v>
       </c>
       <c r="J11">
-        <v>0.61518061409824365</v>
+        <v>0.63003734600639505</v>
       </c>
       <c r="K11">
-        <v>0.61259397278948213</v>
+        <v>0.61194500366852633</v>
       </c>
       <c r="L11">
-        <v>0.61499970103201973</v>
+        <v>0.60855139344580578</v>
       </c>
       <c r="M11">
-        <v>0.60840531277377896</v>
+        <v>0.6122295327549514</v>
       </c>
       <c r="N11">
-        <v>0.5763621375139395</v>
+        <v>0.60308304878303598</v>
       </c>
       <c r="O11">
-        <v>0.55189045193033126</v>
+        <v>0.57178092533128189</v>
       </c>
       <c r="P11">
-        <v>0.53506600607260113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.548598608210353</v>
+      </c>
+      <c r="Q11">
+        <v>0.53146491711541965</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>0.60602989244894845</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C12">
-        <v>0.61569406059274068</v>
+        <v>0.60578222902900691</v>
       </c>
       <c r="D12">
-        <v>0.62434588138550451</v>
+        <v>0.61575804244160359</v>
       </c>
       <c r="E12">
-        <v>0.62586913037001735</v>
+        <v>0.6227675264027992</v>
       </c>
       <c r="F12">
-        <v>0.62739944882645238</v>
+        <v>0.6229822456599462</v>
       </c>
       <c r="G12">
-        <v>0.62619184248825643</v>
+        <v>0.62732839340811952</v>
       </c>
       <c r="H12">
-        <v>0.60586145868533048</v>
+        <v>0.62508433739440794</v>
       </c>
       <c r="I12">
-        <v>0.56390963744461176</v>
+        <v>0.60433823786416285</v>
       </c>
       <c r="J12">
-        <v>0.50060133026763254</v>
+        <v>0.56302119761757541</v>
       </c>
       <c r="K12">
-        <v>0.44503446396380392</v>
+        <v>0.50065472070546013</v>
       </c>
       <c r="L12">
-        <v>0.37991500435092312</v>
+        <v>0.44578416849707247</v>
       </c>
       <c r="M12">
-        <v>0.35609351257699751</v>
+        <v>0.38101662923790158</v>
       </c>
       <c r="N12">
-        <v>0.36327221120671072</v>
+        <v>0.35437506661373253</v>
       </c>
       <c r="O12">
-        <v>0.36560790668901377</v>
+        <v>0.36016943683795483</v>
       </c>
       <c r="P12">
-        <v>0.34160331956620871</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.3611549922842564</v>
+      </c>
+      <c r="Q12">
+        <v>0.33681355636569887</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>0.6013617229270245</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C13">
-        <v>0.59939602475206166</v>
+        <v>0.60202791349036266</v>
       </c>
       <c r="D13">
-        <v>0.6139505216152723</v>
+        <v>0.59986763428894863</v>
       </c>
       <c r="E13">
-        <v>0.62691692171677738</v>
+        <v>0.6099706508058822</v>
       </c>
       <c r="F13">
-        <v>0.5847737735131503</v>
+        <v>0.62452961867005019</v>
       </c>
       <c r="G13">
-        <v>0.56985253718151685</v>
+        <v>0.58020739928380161</v>
       </c>
       <c r="H13">
-        <v>0.56709856060764963</v>
+        <v>0.56478879705651597</v>
       </c>
       <c r="I13">
-        <v>0.54718068630390282</v>
+        <v>0.56149673545954659</v>
       </c>
       <c r="J13">
-        <v>0.4741913594205</v>
+        <v>0.5471126001382548</v>
       </c>
       <c r="K13">
-        <v>0.40700310713276189</v>
+        <v>0.4759316001874187</v>
       </c>
       <c r="L13">
-        <v>0.38458789922796721</v>
+        <v>0.40789735688664391</v>
       </c>
       <c r="M13">
-        <v>0.38001919525823052</v>
+        <v>0.38631202286234079</v>
       </c>
       <c r="N13">
-        <v>0.35730000651735622</v>
+        <v>0.3798120180479006</v>
       </c>
       <c r="O13">
-        <v>0.34323177933675519</v>
+        <v>0.35778237852331068</v>
       </c>
       <c r="P13">
-        <v>0.30808358414177622</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.34842964795712161</v>
+      </c>
+      <c r="Q13">
+        <v>0.31386195043541559</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>0.42756202332283472</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C14">
-        <v>0.58067562374183979</v>
+        <v>0.42703763049190818</v>
       </c>
       <c r="D14">
-        <v>0.62922983508314534</v>
+        <v>0.580047613993387</v>
       </c>
       <c r="E14">
-        <v>0.63783742467895743</v>
+        <v>0.62984990539810637</v>
       </c>
       <c r="F14">
-        <v>0.63718379430473682</v>
+        <v>0.63963018393112137</v>
       </c>
       <c r="G14">
-        <v>0.6512375311325288</v>
+        <v>0.64035501515982474</v>
       </c>
       <c r="H14">
-        <v>0.64143697689322254</v>
+        <v>0.64696396969807946</v>
       </c>
       <c r="I14">
-        <v>0.64533852798775837</v>
+        <v>0.64010653175241039</v>
       </c>
       <c r="J14">
-        <v>0.64153705119786841</v>
+        <v>0.64320779705355302</v>
       </c>
       <c r="K14">
-        <v>0.6295055088754743</v>
+        <v>0.63917247783765807</v>
       </c>
       <c r="L14">
-        <v>0.62593606389587608</v>
+        <v>0.62607399782060513</v>
       </c>
       <c r="M14">
-        <v>0.60553434861671984</v>
+        <v>0.62163879793413857</v>
       </c>
       <c r="N14">
-        <v>0.57858746181924259</v>
+        <v>0.60245302034147352</v>
       </c>
       <c r="O14">
-        <v>0.54343967509602831</v>
+        <v>0.57685031742033888</v>
       </c>
       <c r="P14">
-        <v>0.49829912246047231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.53722974872217533</v>
+      </c>
+      <c r="Q14">
+        <v>0.49287151463582068</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>0.42530013295988528</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C15">
-        <v>0.5775308432203492</v>
+        <v>0.42605504838103059</v>
       </c>
       <c r="D15">
-        <v>0.62597620075396299</v>
+        <v>0.58021368030159892</v>
       </c>
       <c r="E15">
-        <v>0.63593854197808397</v>
+        <v>0.62995230366868538</v>
       </c>
       <c r="F15">
-        <v>0.63410238395435392</v>
+        <v>0.63852435648371064</v>
       </c>
       <c r="G15">
-        <v>0.64844062678064185</v>
+        <v>0.6386506036606292</v>
       </c>
       <c r="H15">
-        <v>0.63572030636818</v>
+        <v>0.65106966560787927</v>
       </c>
       <c r="I15">
-        <v>0.64117407084662936</v>
+        <v>0.64220276479517835</v>
       </c>
       <c r="J15">
-        <v>0.63900286778699555</v>
+        <v>0.64609623401598804</v>
       </c>
       <c r="K15">
-        <v>0.62486898559571413</v>
+        <v>0.6414318142539237</v>
       </c>
       <c r="L15">
-        <v>0.61971149701643546</v>
+        <v>0.62976739415489735</v>
       </c>
       <c r="M15">
-        <v>0.599622696966994</v>
+        <v>0.6259454348635255</v>
       </c>
       <c r="N15">
-        <v>0.56637542295050514</v>
+        <v>0.60341401779735238</v>
       </c>
       <c r="O15">
-        <v>0.54093858255191019</v>
+        <v>0.57227178058265649</v>
       </c>
       <c r="P15">
-        <v>0.52912244952151466</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.54830718287662672</v>
+      </c>
+      <c r="Q15">
+        <v>0.53176276977478054</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>0.42613012091518648</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C16">
-        <v>0.57941662880811129</v>
+        <v>0.42730276212907509</v>
       </c>
       <c r="D16">
-        <v>0.62646522155064832</v>
+        <v>0.58081994904212764</v>
       </c>
       <c r="E16">
-        <v>0.63561847429163632</v>
+        <v>0.62877803106564667</v>
       </c>
       <c r="F16">
-        <v>0.63427422239314157</v>
+        <v>0.63751371341429386</v>
       </c>
       <c r="G16">
-        <v>0.64639152990556625</v>
+        <v>0.63677206340452064</v>
       </c>
       <c r="H16">
-        <v>0.63749404318819569</v>
+        <v>0.64836851336877976</v>
       </c>
       <c r="I16">
-        <v>0.64066923482992233</v>
+        <v>0.63993300151179011</v>
       </c>
       <c r="J16">
-        <v>0.63602346521614661</v>
+        <v>0.64464819685302055</v>
       </c>
       <c r="K16">
-        <v>0.622103070478774</v>
+        <v>0.64150774360560858</v>
       </c>
       <c r="L16">
-        <v>0.61981535700011614</v>
+        <v>0.62926976910791699</v>
       </c>
       <c r="M16">
-        <v>0.59068904644538878</v>
+        <v>0.62388104724725135</v>
       </c>
       <c r="N16">
-        <v>0.55366165167702919</v>
+        <v>0.59382836754672153</v>
       </c>
       <c r="O16">
-        <v>0.52527002682474389</v>
+        <v>0.55473173887721139</v>
       </c>
       <c r="P16">
-        <v>0.51931421257798938</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.52661018346158439</v>
+      </c>
+      <c r="Q16">
+        <v>0.51754139883036154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>0.42685065576084641</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C17">
-        <v>0.58063459906272763</v>
+        <v>0.42601904477445718</v>
       </c>
       <c r="D17">
-        <v>0.63006163768375012</v>
+        <v>0.5788472021576665</v>
       </c>
       <c r="E17">
-        <v>0.63892197097248626</v>
+        <v>0.62597738440651252</v>
       </c>
       <c r="F17">
-        <v>0.63899364198543851</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0.65131686583041992</v>
+        <v>0.63427604883990107</v>
+      </c>
+      <c r="G17">
+        <v>0.63344232907960418</v>
       </c>
       <c r="H17">
-        <v>0.64223218573229246</v>
+        <v>0.64658076432822553</v>
       </c>
       <c r="I17">
-        <v>0.6462053240083323</v>
+        <v>0.63687332868466051</v>
       </c>
       <c r="J17">
-        <v>0.6422968087600045</v>
+        <v>0.64207403660381968</v>
       </c>
       <c r="K17">
-        <v>0.62838478044718071</v>
+        <v>0.63940071791959796</v>
       </c>
       <c r="L17">
-        <v>0.62575069386771209</v>
+        <v>0.62672857244039848</v>
       </c>
       <c r="M17">
-        <v>0.59138768786062967</v>
+        <v>0.62546340742474016</v>
       </c>
       <c r="N17">
-        <v>0.55553856801748414</v>
+        <v>0.59220389466037893</v>
       </c>
       <c r="O17">
-        <v>0.52480185336253227</v>
+        <v>0.55737170641110045</v>
       </c>
       <c r="P17">
-        <v>0.5159982508490869</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.52702860958912368</v>
+      </c>
+      <c r="Q17">
+        <v>0.51897332051095035</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18">
-        <v>0.60565975128581984</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C18">
-        <v>0.61164913359819262</v>
+        <v>0.60489862142506601</v>
       </c>
       <c r="D18">
-        <v>0.61892838079679913</v>
+        <v>0.61367211497714302</v>
       </c>
       <c r="E18">
-        <v>0.61588993484765564</v>
+        <v>0.61696818843617385</v>
       </c>
       <c r="F18">
-        <v>0.62627034635658763</v>
+        <v>0.6121619869315863</v>
       </c>
       <c r="G18">
-        <v>0.61227624129537017</v>
+        <v>0.62516233754339734</v>
       </c>
       <c r="H18">
-        <v>0.6009020469045655</v>
+        <v>0.60893024514084371</v>
       </c>
       <c r="I18">
-        <v>0.56183312872457003</v>
+        <v>0.59857439546197633</v>
       </c>
       <c r="J18">
-        <v>0.50500189926235095</v>
+        <v>0.56359843504509144</v>
       </c>
       <c r="K18">
-        <v>0.44780970194695818</v>
+        <v>0.50700801102855475</v>
       </c>
       <c r="L18">
-        <v>0.39765804323963372</v>
+        <v>0.45272863895289989</v>
       </c>
       <c r="M18">
-        <v>0.37871910819733862</v>
+        <v>0.40456249023591973</v>
       </c>
       <c r="N18">
-        <v>0.38100583664286652</v>
+        <v>0.38538258748334009</v>
       </c>
       <c r="O18">
-        <v>0.38445134325802932</v>
+        <v>0.38540808811797622</v>
       </c>
       <c r="P18">
-        <v>0.38738239722624579</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.38996377743815402</v>
+      </c>
+      <c r="Q18">
+        <v>0.39314173975792038</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>0.60183731026245191</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C19">
-        <v>0.61184481389141121</v>
+        <v>0.60310769773121375</v>
       </c>
       <c r="D19">
-        <v>0.6240889475779241</v>
+        <v>0.61270776676430927</v>
       </c>
       <c r="E19">
-        <v>0.62938030761554986</v>
+        <v>0.6245144485342744</v>
       </c>
       <c r="F19">
-        <v>0.64800136302198919</v>
+        <v>0.63236218042075609</v>
       </c>
       <c r="G19">
-        <v>0.6246942533046218</v>
+        <v>0.64871227847095869</v>
       </c>
       <c r="H19">
-        <v>0.62449784897773875</v>
+        <v>0.6259045337923751</v>
       </c>
       <c r="I19">
-        <v>0.59715935763864458</v>
+        <v>0.62497694504954115</v>
       </c>
       <c r="J19">
-        <v>0.56295929565763136</v>
+        <v>0.60113477610301147</v>
       </c>
       <c r="K19">
-        <v>0.52736181172662744</v>
+        <v>0.56709493374360642</v>
       </c>
       <c r="L19">
-        <v>0.48999524858635751</v>
+        <v>0.53011852604366982</v>
       </c>
       <c r="M19">
-        <v>0.46604232871057522</v>
+        <v>0.49300182663685549</v>
       </c>
       <c r="N19">
-        <v>0.44220900437561861</v>
+        <v>0.46903041681538371</v>
       </c>
       <c r="O19">
-        <v>0.42761853019651319</v>
+        <v>0.44424874766177508</v>
       </c>
       <c r="P19">
-        <v>0.41083711680640039</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.43140770900454822</v>
+      </c>
+      <c r="Q19">
+        <v>0.4159662574872327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>0.60248470194912462</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C20">
-        <v>0.61464980714984263</v>
+        <v>0.60196001977856539</v>
       </c>
       <c r="D20">
-        <v>0.63425022807502418</v>
+        <v>0.61581922173616277</v>
       </c>
       <c r="E20">
-        <v>0.63458337990160529</v>
+        <v>0.63627585581383128</v>
       </c>
       <c r="F20">
-        <v>0.64751937601727927</v>
+        <v>0.63887343100844041</v>
       </c>
       <c r="G20">
-        <v>0.64802751750087373</v>
+        <v>0.65019163308977634</v>
       </c>
       <c r="H20">
-        <v>0.63011271456904505</v>
+        <v>0.65083937302508998</v>
       </c>
       <c r="I20">
-        <v>0.60045132213966246</v>
+        <v>0.63561040026972804</v>
       </c>
       <c r="J20">
-        <v>0.57834987024535212</v>
+        <v>0.60636209626617821</v>
       </c>
       <c r="K20">
-        <v>0.568090239594917</v>
+        <v>0.58275101427765275</v>
       </c>
       <c r="L20">
-        <v>0.53695287727833285</v>
+        <v>0.56993484271671502</v>
       </c>
       <c r="M20">
-        <v>0.51325653106430447</v>
+        <v>0.54451619918646166</v>
       </c>
       <c r="N20">
-        <v>0.50842788285519558</v>
+        <v>0.51941732173490718</v>
       </c>
       <c r="O20">
-        <v>0.48389456123500463</v>
+        <v>0.51301311626419122</v>
       </c>
       <c r="P20">
-        <v>0.46157838667619849</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.48688226460154821</v>
+      </c>
+      <c r="Q20">
+        <v>0.46154251764060389</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>0.46056069113887732</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C21">
-        <v>0.59377099379164422</v>
+        <v>0.46211591792587958</v>
       </c>
       <c r="D21">
-        <v>0.58243857991319303</v>
+        <v>0.59472972432286342</v>
       </c>
       <c r="E21">
-        <v>0.543254248380726</v>
+        <v>0.58244290795904397</v>
       </c>
       <c r="F21">
-        <v>0.57511569480514024</v>
+        <v>0.54189837506674243</v>
       </c>
       <c r="G21">
-        <v>0.56496837036468894</v>
+        <v>0.57473399263896807</v>
       </c>
       <c r="H21">
-        <v>0.50743136403291422</v>
+        <v>0.56888220602867823</v>
       </c>
       <c r="I21">
-        <v>0.43523994569941499</v>
+        <v>0.50762965438060348</v>
       </c>
       <c r="J21">
-        <v>0.41770183604947853</v>
+        <v>0.44573815868920891</v>
       </c>
       <c r="K21">
-        <v>0.38258887657077179</v>
+        <v>0.42524499633752721</v>
       </c>
       <c r="L21">
-        <v>0.37127485549554018</v>
+        <v>0.39066407720763502</v>
       </c>
       <c r="M21">
-        <v>0.36053172540882389</v>
+        <v>0.37826370125301018</v>
       </c>
       <c r="N21">
-        <v>0.36134888371251761</v>
+        <v>0.36468629162149491</v>
       </c>
       <c r="O21">
-        <v>0.36573853852147659</v>
+        <v>0.36673108617094419</v>
       </c>
       <c r="P21">
-        <v>0.34527075502538462</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.37224624040022591</v>
+      </c>
+      <c r="Q21">
+        <v>0.35402625361168011</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22">
-        <v>0.45717635585135807</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C22">
-        <v>0.59046985324581513</v>
+        <v>0.45910909807390538</v>
       </c>
       <c r="D22">
-        <v>0.57957769323131103</v>
+        <v>0.5931609557927251</v>
       </c>
       <c r="E22">
-        <v>0.53972680608161816</v>
+        <v>0.58306503292145573</v>
       </c>
       <c r="F22">
-        <v>0.57243248550062775</v>
+        <v>0.54210993178928912</v>
       </c>
       <c r="G22">
-        <v>0.57191978193566195</v>
+        <v>0.57282906179320014</v>
       </c>
       <c r="H22">
-        <v>0.50233192407508565</v>
+        <v>0.57558559538832155</v>
       </c>
       <c r="I22">
-        <v>0.43768177246937467</v>
+        <v>0.50838991626694063</v>
       </c>
       <c r="J22">
-        <v>0.40471475792127659</v>
+        <v>0.44801684740476472</v>
       </c>
       <c r="K22">
-        <v>0.38595113802934589</v>
+        <v>0.41532735311570229</v>
       </c>
       <c r="L22">
-        <v>0.3629819419130127</v>
+        <v>0.40126506084881591</v>
       </c>
       <c r="M22">
-        <v>0.35838451808417721</v>
+        <v>0.38027298544608978</v>
       </c>
       <c r="N22">
-        <v>0.37009959714313528</v>
+        <v>0.37652040233372153</v>
       </c>
       <c r="O22">
-        <v>0.37218499487125128</v>
+        <v>0.38802333858801158</v>
       </c>
       <c r="P22">
-        <v>0.3395916045512426</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.39271956590512852</v>
+      </c>
+      <c r="Q22">
+        <v>0.35603669187811759</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23">
-        <v>0.59940262489573037</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C23">
-        <v>0.59656438033839332</v>
+        <v>0.59857063444073644</v>
       </c>
       <c r="D23">
-        <v>0.57707604678647573</v>
+        <v>0.59737036929116172</v>
       </c>
       <c r="E23">
-        <v>0.60034711953323328</v>
+        <v>0.57779956864228321</v>
       </c>
       <c r="F23">
-        <v>0.54109242064791419</v>
+        <v>0.59853871963405314</v>
       </c>
       <c r="G23">
-        <v>0.48671573821599218</v>
+        <v>0.54117847410842435</v>
       </c>
       <c r="H23">
-        <v>0.42389221024374218</v>
+        <v>0.49669656026459741</v>
       </c>
       <c r="I23">
-        <v>0.40534091994681298</v>
+        <v>0.42926078771710152</v>
       </c>
       <c r="J23">
-        <v>0.41320554703964729</v>
+        <v>0.41155146532415032</v>
       </c>
       <c r="K23">
-        <v>0.37449604019364091</v>
+        <v>0.42086760214329338</v>
       </c>
       <c r="L23">
-        <v>0.35042743483942601</v>
+        <v>0.37980828290537483</v>
       </c>
       <c r="M23">
-        <v>0.32785918255153118</v>
+        <v>0.35480160723692949</v>
       </c>
       <c r="N23">
-        <v>0.29955159602167442</v>
+        <v>0.3363616891133186</v>
       </c>
       <c r="O23">
-        <v>0.29157892217266629</v>
+        <v>0.30779795861081538</v>
       </c>
       <c r="P23">
-        <v>0.26471536819483282</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.29671222235118311</v>
+      </c>
+      <c r="Q23">
+        <v>0.26878094457865648</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24">
-        <v>0.13646587638044849</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C24">
-        <v>0.17961926635484671</v>
+        <v>0.1382554658385588</v>
       </c>
       <c r="D24">
-        <v>0.21005244891916061</v>
+        <v>0.17915192293124951</v>
       </c>
       <c r="E24">
-        <v>0.17559971215180939</v>
+        <v>0.2065336884868893</v>
       </c>
       <c r="F24">
-        <v>5.1937442030884268E-2</v>
+        <v>0.17594938887564551</v>
       </c>
       <c r="G24">
-        <v>6.5679940712417215E-2</v>
+        <v>5.794921931254747E-2</v>
       </c>
       <c r="H24">
-        <v>-5.8680091987873759E-3</v>
+        <v>7.2375162602698162E-2</v>
       </c>
       <c r="I24">
-        <v>-0.1184249488333852</v>
+        <v>7.9702089011233889E-3</v>
       </c>
       <c r="J24">
-        <v>-0.24152266894627691</v>
+        <v>-9.6025010179702636E-2</v>
       </c>
       <c r="K24">
-        <v>-0.33648366068100227</v>
+        <v>-0.22300105399218309</v>
       </c>
       <c r="L24">
-        <v>-0.33523878590451478</v>
+        <v>-0.30779283956946041</v>
       </c>
       <c r="M24">
-        <v>-0.32333610045995231</v>
+        <v>-0.31153164613013112</v>
       </c>
       <c r="N24">
-        <v>-0.28350712206340473</v>
+        <v>-0.31049949776171482</v>
       </c>
       <c r="O24">
-        <v>-0.25523366048716439</v>
+        <v>-0.25510976634328519</v>
       </c>
       <c r="P24">
-        <v>-0.26019846950368308</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.22276756725199279</v>
+      </c>
+      <c r="Q24">
+        <v>-0.2264129336324785</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25">
-        <v>0.10311470576919091</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C25">
-        <v>0.1212463455480407</v>
+        <v>0.1071061921295369</v>
       </c>
       <c r="D25">
-        <v>0.12392633809589571</v>
+        <v>0.13104513516659569</v>
       </c>
       <c r="E25">
-        <v>0.14678839060254309</v>
+        <v>0.13575440869955621</v>
       </c>
       <c r="F25">
-        <v>0.13617799300830311</v>
+        <v>0.15321202809935819</v>
       </c>
       <c r="G25">
-        <v>2.7982030492031441E-2</v>
+        <v>0.14136103425941621</v>
       </c>
       <c r="H25">
-        <v>-8.8617190172996935E-2</v>
+        <v>3.7836767815972248E-2</v>
       </c>
       <c r="I25">
-        <v>-0.24313913610871091</v>
+        <v>-8.3379014104155977E-2</v>
       </c>
       <c r="J25">
-        <v>-0.40185086391737301</v>
+        <v>-0.22591961583337439</v>
       </c>
       <c r="K25">
-        <v>-0.52394989838739514</v>
+        <v>-0.38203705898521212</v>
       </c>
       <c r="L25">
-        <v>-0.6494940350073708</v>
+        <v>-0.50660774267303577</v>
       </c>
       <c r="M25">
-        <v>-0.76753777517519206</v>
+        <v>-0.6433355192514939</v>
       </c>
       <c r="N25">
-        <v>-0.84381200517892085</v>
+        <v>-0.77612549586765534</v>
       </c>
       <c r="O25">
-        <v>-0.92875265648956007</v>
+        <v>-0.84996384693485416</v>
       </c>
       <c r="P25">
-        <v>-0.96513292021831287</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.93292954409867945</v>
+      </c>
+      <c r="Q25">
+        <v>-0.97556729914787044</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>0.1162372465463285</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C26">
-        <v>0.14937669148420959</v>
+        <v>0.1183952588670345</v>
       </c>
       <c r="D26">
-        <v>0.180318521202389</v>
+        <v>0.15421444015442681</v>
       </c>
       <c r="E26">
-        <v>0.1996428822411262</v>
+        <v>0.18525679420806049</v>
       </c>
       <c r="F26">
-        <v>0.1858967929546203</v>
+        <v>0.2025042704186861</v>
       </c>
       <c r="G26">
-        <v>0.16564736692352069</v>
+        <v>0.18420383457567061</v>
       </c>
       <c r="H26">
-        <v>0.12577596139145919</v>
+        <v>0.15690236250250689</v>
       </c>
       <c r="I26">
-        <v>0.1261310612757538</v>
+        <v>0.1237365430811897</v>
       </c>
       <c r="J26">
-        <v>0.12043765889431</v>
+        <v>0.1177829598408337</v>
       </c>
       <c r="K26">
-        <v>0.12033784693805689</v>
+        <v>0.121224238483578</v>
       </c>
       <c r="L26">
-        <v>8.3591843770012664E-2</v>
+        <v>0.1150367842969004</v>
       </c>
       <c r="M26">
-        <v>6.9561172591801418E-2</v>
+        <v>9.090658271937356E-2</v>
       </c>
       <c r="N26">
-        <v>-5.4001018556718312E-3</v>
+        <v>6.1078917287262557E-2</v>
       </c>
       <c r="O26">
-        <v>-1.2457842352856919E-2</v>
+        <v>-1.40512531861531E-2</v>
       </c>
       <c r="P26">
-        <v>-4.839990693857428E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-1.979093866069748E-2</v>
+      </c>
+      <c r="Q26">
+        <v>-6.0509227014555932E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>9.2926137410823353E-2</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C27">
-        <v>0.12776848215962069</v>
+        <v>9.032641339285305E-2</v>
       </c>
       <c r="D27">
-        <v>0.17862128551900719</v>
+        <v>0.123644724313102</v>
       </c>
       <c r="E27">
-        <v>0.22814812129542381</v>
+        <v>0.17951268746540841</v>
       </c>
       <c r="F27">
-        <v>0.1939810379413244</v>
+        <v>0.22521188643653189</v>
       </c>
       <c r="G27">
-        <v>0.13150926237101351</v>
+        <v>0.1920295845111086</v>
       </c>
       <c r="H27">
-        <v>0.1090401115870841</v>
+        <v>0.12524887881017119</v>
       </c>
       <c r="I27">
-        <v>8.9200777331498587E-2</v>
+        <v>0.1001706954284209</v>
       </c>
       <c r="J27">
-        <v>7.5619456524686379E-2</v>
+        <v>7.855488531364295E-2</v>
       </c>
       <c r="K27">
-        <v>6.0414300668692543E-2</v>
+        <v>6.3634167752307541E-2</v>
       </c>
       <c r="L27">
-        <v>3.7171676122168283E-2</v>
+        <v>5.4895156565319833E-2</v>
       </c>
       <c r="M27">
-        <v>-2.9070995377954351E-2</v>
+        <v>3.2024439732663203E-2</v>
       </c>
       <c r="N27">
-        <v>-7.9188764833268852E-2</v>
+        <v>-3.1124878256998442E-2</v>
       </c>
       <c r="O27">
-        <v>-0.1745515510257537</v>
+        <v>-8.0753118840822632E-2</v>
       </c>
       <c r="P27">
-        <v>-0.26411238117334201</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.17131624654979069</v>
+      </c>
+      <c r="Q27">
+        <v>-0.25547553394923839</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28">
-        <v>0.59416949182009382</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C28">
-        <v>0.6267260854111546</v>
+        <v>0.59419350090933742</v>
       </c>
       <c r="D28">
-        <v>0.60239524449479964</v>
+        <v>0.6265482244614089</v>
       </c>
       <c r="E28">
-        <v>0.62270867628498872</v>
+        <v>0.6030351253473516</v>
       </c>
       <c r="F28">
-        <v>0.61938282220916441</v>
+        <v>0.62137421883587152</v>
       </c>
       <c r="G28">
-        <v>0.62592839276883538</v>
+        <v>0.61855192067880671</v>
       </c>
       <c r="H28">
-        <v>0.6083507876437092</v>
+        <v>0.62395062509966481</v>
       </c>
       <c r="I28">
-        <v>0.58985121146109332</v>
+        <v>0.60578451293890268</v>
       </c>
       <c r="J28">
-        <v>0.59878533586505189</v>
+        <v>0.58671656712206632</v>
       </c>
       <c r="K28">
-        <v>0.58890527589685004</v>
+        <v>0.59460659954284623</v>
       </c>
       <c r="L28">
-        <v>0.56452213731480361</v>
+        <v>0.5869640463977065</v>
       </c>
       <c r="M28">
-        <v>0.51552074916922785</v>
+        <v>0.5659660640913482</v>
       </c>
       <c r="N28">
-        <v>0.48056047258712181</v>
+        <v>0.51727552250408237</v>
       </c>
       <c r="O28">
-        <v>0.42007937746634649</v>
+        <v>0.48391503666187391</v>
       </c>
       <c r="P28">
-        <v>0.36095588453125671</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.42544977336745082</v>
+      </c>
+      <c r="Q28">
+        <v>0.36740037801607228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29">
-        <v>0.5970985455298754</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C29">
-        <v>0.62909260722071658</v>
+        <v>0.5987249016142806</v>
       </c>
       <c r="D29">
-        <v>0.60399755758060314</v>
+        <v>0.63040204588104687</v>
       </c>
       <c r="E29">
-        <v>0.62231601428679673</v>
+        <v>0.60539676329811254</v>
       </c>
       <c r="F29">
-        <v>0.60974474580515325</v>
+        <v>0.62437746584595188</v>
       </c>
       <c r="G29">
-        <v>0.58496922644468874</v>
+        <v>0.61280549487958669</v>
       </c>
       <c r="H29">
-        <v>0.55412398535806673</v>
+        <v>0.59088448325046883</v>
       </c>
       <c r="I29">
-        <v>0.56509877484310411</v>
+        <v>0.55983595202222225</v>
       </c>
       <c r="J29">
-        <v>0.56217181870866795</v>
+        <v>0.57235108916963928</v>
       </c>
       <c r="K29">
-        <v>0.57793619973644583</v>
+        <v>0.56412832188391704</v>
       </c>
       <c r="L29">
-        <v>0.55949069571006638</v>
+        <v>0.57758373067756497</v>
       </c>
       <c r="M29">
-        <v>0.53047899411325139</v>
+        <v>0.5530391988030845</v>
       </c>
       <c r="N29">
-        <v>0.48187614095594877</v>
+        <v>0.52128633663327228</v>
       </c>
       <c r="O29">
-        <v>0.44743815978085472</v>
+        <v>0.47260839323936221</v>
       </c>
       <c r="P29">
-        <v>0.38337679536739683</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.43247322148881268</v>
+      </c>
+      <c r="Q29">
+        <v>0.36607292292087901</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30">
-        <v>0.62534913678672532</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C30">
-        <v>0.629866566388946</v>
+        <v>0.62521784081969123</v>
       </c>
       <c r="D30">
-        <v>0.61008328574557291</v>
+        <v>0.62987543469901419</v>
       </c>
       <c r="E30">
-        <v>0.62660063985875392</v>
+        <v>0.61061751512657758</v>
       </c>
       <c r="F30">
-        <v>0.62190131314222752</v>
+        <v>0.62645610071401425</v>
       </c>
       <c r="G30">
-        <v>0.62699301915361527</v>
+        <v>0.62332134601907996</v>
       </c>
       <c r="H30">
-        <v>0.60971231663194914</v>
+        <v>0.62469855439097621</v>
       </c>
       <c r="I30">
-        <v>0.59168607671108364</v>
+        <v>0.60989916518100662</v>
       </c>
       <c r="J30">
-        <v>0.58733720858295713</v>
+        <v>0.58586856750671734</v>
       </c>
       <c r="K30">
-        <v>0.58013031023080475</v>
+        <v>0.58442144823377284</v>
       </c>
       <c r="L30">
-        <v>0.54518595410426718</v>
+        <v>0.57594333681185639</v>
       </c>
       <c r="M30">
-        <v>0.50609182847227108</v>
+        <v>0.54173354546552965</v>
       </c>
       <c r="N30">
-        <v>0.45124085387085111</v>
+        <v>0.49998256512123251</v>
       </c>
       <c r="O30">
-        <v>0.39747061650246879</v>
+        <v>0.44207455432032772</v>
       </c>
       <c r="P30">
-        <v>0.29593840185447828</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.38688863936112011</v>
+      </c>
+      <c r="Q30">
+        <v>0.28582526436175121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31">
-        <v>0.62418293013183146</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C31">
-        <v>0.62832711165682065</v>
+        <v>0.62583181307683577</v>
       </c>
       <c r="D31">
-        <v>0.6087288832177723</v>
+        <v>0.63015441774435543</v>
       </c>
       <c r="E31">
-        <v>0.62301368669507395</v>
+        <v>0.61064828754187694</v>
       </c>
       <c r="F31">
-        <v>0.62035731689378748</v>
+        <v>0.6262531529026506</v>
       </c>
       <c r="G31">
-        <v>0.62418492914384438</v>
+        <v>0.62237927829247452</v>
       </c>
       <c r="H31">
-        <v>0.61966564722344641</v>
+        <v>0.62807294037467842</v>
       </c>
       <c r="I31">
-        <v>0.60891828593099373</v>
+        <v>0.62282788127359823</v>
       </c>
       <c r="J31">
-        <v>0.61716136595486815</v>
+        <v>0.6160662269467897</v>
       </c>
       <c r="K31">
-        <v>0.6280418482370782</v>
+        <v>0.62135345497646344</v>
       </c>
       <c r="L31">
-        <v>0.6249967826997268</v>
+        <v>0.63207382781649835</v>
       </c>
       <c r="M31">
-        <v>0.6097871839617568</v>
+        <v>0.62816169752379925</v>
       </c>
       <c r="N31">
-        <v>0.57727277789001996</v>
+        <v>0.61046955760493249</v>
       </c>
       <c r="O31">
-        <v>0.57246908796649143</v>
+        <v>0.57703601877648691</v>
       </c>
       <c r="P31">
-        <v>0.49995992237128001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.57385161032075516</v>
+      </c>
+      <c r="Q31">
+        <v>0.49887931566800708</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B32">
-        <v>0.59795236872264068</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C32">
-        <v>0.62911488269952343</v>
+        <v>0.59737521730402976</v>
       </c>
       <c r="D32">
-        <v>0.60244582747264974</v>
+        <v>0.62910880162603855</v>
       </c>
       <c r="E32">
-        <v>0.62012874648506411</v>
+        <v>0.60308839749857179</v>
       </c>
       <c r="F32">
-        <v>0.61103924483607475</v>
+        <v>0.62264414100801946</v>
       </c>
       <c r="G32">
-        <v>0.59487285317582095</v>
+        <v>0.61336004895078311</v>
       </c>
       <c r="H32">
-        <v>0.57361330710409875</v>
+        <v>0.59871826588189614</v>
       </c>
       <c r="I32">
-        <v>0.58724827960785753</v>
+        <v>0.57890932453255051</v>
       </c>
       <c r="J32">
-        <v>0.59235856375148555</v>
+        <v>0.59560173816163697</v>
       </c>
       <c r="K32">
-        <v>0.60650757422646806</v>
+        <v>0.59747941058644827</v>
       </c>
       <c r="L32">
-        <v>0.60475240973183553</v>
+        <v>0.60983952325054314</v>
       </c>
       <c r="M32">
-        <v>0.59374762755025945</v>
+        <v>0.60519157354360364</v>
       </c>
       <c r="N32">
-        <v>0.56436697297704064</v>
+        <v>0.59581821439618832</v>
       </c>
       <c r="O32">
-        <v>0.55540284046595945</v>
+        <v>0.56535404976155557</v>
       </c>
       <c r="P32">
-        <v>0.51973370699574373</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.55479846640496489</v>
+      </c>
+      <c r="Q32">
+        <v>0.51854441218532521</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>0.59765707236488652</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C33">
-        <v>0.6293631285085447</v>
+        <v>0.59674339421793376</v>
       </c>
       <c r="D33">
-        <v>0.60560163948732448</v>
+        <v>0.63008871256249954</v>
       </c>
       <c r="E33">
-        <v>0.62382153744127844</v>
+        <v>0.60520964633574115</v>
       </c>
       <c r="F33">
-        <v>0.61526054463230084</v>
+        <v>0.62197572909548104</v>
       </c>
       <c r="G33">
-        <v>0.60112022473239912</v>
+        <v>0.61222660149129549</v>
       </c>
       <c r="H33">
-        <v>0.58388829011396859</v>
+        <v>0.59504321410907679</v>
       </c>
       <c r="I33">
-        <v>0.59050546201617593</v>
+        <v>0.57798479355324528</v>
       </c>
       <c r="J33">
-        <v>0.59375541702447365</v>
+        <v>0.5878920991299369</v>
       </c>
       <c r="K33">
-        <v>0.61232468311372368</v>
+        <v>0.58946693660861671</v>
       </c>
       <c r="L33">
-        <v>0.60955926196446886</v>
+        <v>0.60885279990845809</v>
       </c>
       <c r="M33">
-        <v>0.59970505774015137</v>
+        <v>0.60850839286236003</v>
       </c>
       <c r="N33">
-        <v>0.57061644676842216</v>
+        <v>0.59961329009376341</v>
       </c>
       <c r="O33">
-        <v>0.5693180980846968</v>
+        <v>0.57175532608750756</v>
       </c>
       <c r="P33">
-        <v>0.53229719297749467</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.56688241442003329</v>
+      </c>
+      <c r="Q33">
+        <v>0.53236027795051899</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B34">
-        <v>0.59648997362881662</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C34">
-        <v>0.6281812319179122</v>
+        <v>0.59600117203513614</v>
       </c>
       <c r="D34">
-        <v>0.60306882067522671</v>
+        <v>0.62762369621550695</v>
       </c>
       <c r="E34">
-        <v>0.62018671495495192</v>
+        <v>0.60112067779781575</v>
       </c>
       <c r="F34">
-        <v>0.61003083803892233</v>
+        <v>0.61709235639310234</v>
       </c>
       <c r="G34">
-        <v>0.59489608291869411</v>
+        <v>0.60790237025409266</v>
       </c>
       <c r="H34">
-        <v>0.58001650933122695</v>
+        <v>0.59191969313428772</v>
       </c>
       <c r="I34">
-        <v>0.59598116762940323</v>
+        <v>0.5747819181927849</v>
       </c>
       <c r="J34">
-        <v>0.59700995538611235</v>
+        <v>0.58728350134622942</v>
       </c>
       <c r="K34">
-        <v>0.61037487091455744</v>
+        <v>0.59208948636332037</v>
       </c>
       <c r="L34">
-        <v>0.60976189962631633</v>
+        <v>0.60687022026385118</v>
       </c>
       <c r="M34">
-        <v>0.60340262072785766</v>
+        <v>0.60772730584018031</v>
       </c>
       <c r="N34">
-        <v>0.58323037517359799</v>
+        <v>0.59831364366659257</v>
       </c>
       <c r="O34">
-        <v>0.57604538079599632</v>
+        <v>0.57591647813444324</v>
       </c>
       <c r="P34">
-        <v>0.54743718709403177</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.57179137959819759</v>
+      </c>
+      <c r="Q34">
+        <v>0.54219091022893873</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>0.59801283123014171</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C35">
-        <v>0.63069927943677517</v>
+        <v>0.59677644979927247</v>
       </c>
       <c r="D35">
-        <v>0.60587785176133901</v>
+        <v>0.6297947033509449</v>
       </c>
       <c r="E35">
-        <v>0.62511967968920013</v>
+        <v>0.6055582216908052</v>
       </c>
       <c r="F35">
-        <v>0.61534770509334247</v>
+        <v>0.62248470354923802</v>
       </c>
       <c r="G35">
-        <v>0.60203249234695322</v>
+        <v>0.61194540219684956</v>
       </c>
       <c r="H35">
-        <v>0.58685599981301784</v>
+        <v>0.59345452927551379</v>
       </c>
       <c r="I35">
-        <v>0.59904000159350734</v>
+        <v>0.57713644998258107</v>
       </c>
       <c r="J35">
-        <v>0.59502138352855471</v>
+        <v>0.58948132920571683</v>
       </c>
       <c r="K35">
-        <v>0.61273721586719243</v>
+        <v>0.58925287137094839</v>
       </c>
       <c r="L35">
-        <v>0.61083423149348426</v>
+        <v>0.60736385596547449</v>
       </c>
       <c r="M35">
-        <v>0.6090410021398408</v>
+        <v>0.60602381329562105</v>
       </c>
       <c r="N35">
-        <v>0.58793765696090605</v>
+        <v>0.60393918599691576</v>
       </c>
       <c r="O35">
-        <v>0.58555342624224527</v>
+        <v>0.58376226484504834</v>
       </c>
       <c r="P35">
-        <v>0.56399593518237168</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.58017531390969457</v>
+      </c>
+      <c r="Q35">
+        <v>0.55853582772513399</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B36">
-        <v>0.59802956703725807</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C36">
-        <v>0.63001638742073818</v>
+        <v>0.59726682577077328</v>
       </c>
       <c r="D36">
-        <v>0.60618546506463811</v>
+        <v>0.62956780580029181</v>
       </c>
       <c r="E36">
-        <v>0.62156052914455662</v>
+        <v>0.60584747054161292</v>
       </c>
       <c r="F36">
-        <v>0.6136043242957685</v>
+        <v>0.62365099272206581</v>
       </c>
       <c r="G36">
-        <v>0.59672864412988846</v>
+        <v>0.61385813542240553</v>
       </c>
       <c r="H36">
-        <v>0.57661727260604101</v>
+        <v>0.59960783829176845</v>
       </c>
       <c r="I36">
-        <v>0.59011826307581217</v>
+        <v>0.57962197998473253</v>
       </c>
       <c r="J36">
-        <v>0.59316546649696811</v>
+        <v>0.590443479560953</v>
       </c>
       <c r="K36">
-        <v>0.61188403969878091</v>
+        <v>0.5888360596709189</v>
       </c>
       <c r="L36">
-        <v>0.60503008562465044</v>
+        <v>0.61043058907584891</v>
       </c>
       <c r="M36">
-        <v>0.59116698511690335</v>
+        <v>0.60677722385555322</v>
       </c>
       <c r="N36">
-        <v>0.55931046846313814</v>
+        <v>0.59124056835719963</v>
       </c>
       <c r="O36">
-        <v>0.56187860154990521</v>
+        <v>0.56176415040494765</v>
       </c>
       <c r="P36">
-        <v>0.53637977607881704</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.56572146126479816</v>
+      </c>
+      <c r="Q36">
+        <v>0.53527935683246464</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>0.59890133126169509</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C37">
-        <v>0.63133279755790261</v>
+        <v>0.5978821017815672</v>
       </c>
       <c r="D37">
-        <v>0.60950503118093857</v>
+        <v>0.6299326621702015</v>
       </c>
       <c r="E37">
-        <v>0.6252737814678988</v>
+        <v>0.60590315711243314</v>
       </c>
       <c r="F37">
-        <v>0.61525393214378832</v>
+        <v>0.62338528542447913</v>
       </c>
       <c r="G37">
-        <v>0.59999220091175542</v>
+        <v>0.61414417628848106</v>
       </c>
       <c r="H37">
-        <v>0.58073263277982023</v>
+        <v>0.59836293049694256</v>
       </c>
       <c r="I37">
-        <v>0.59359082820271047</v>
+        <v>0.57979443172819667</v>
       </c>
       <c r="J37">
-        <v>0.59828860890541147</v>
+        <v>0.59324524896458508</v>
       </c>
       <c r="K37">
-        <v>0.61835051700800958</v>
+        <v>0.59516680290880464</v>
       </c>
       <c r="L37">
-        <v>0.61107771051434234</v>
+        <v>0.61478254720714764</v>
       </c>
       <c r="M37">
-        <v>0.59748773460187621</v>
+        <v>0.60822666159500338</v>
       </c>
       <c r="N37">
-        <v>0.57435768502898588</v>
+        <v>0.59877059474770222</v>
       </c>
       <c r="O37">
-        <v>0.57721748641915771</v>
+        <v>0.5739534259971083</v>
       </c>
       <c r="P37">
-        <v>0.55105824819613103</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.5758480402949786</v>
+      </c>
+      <c r="Q37">
+        <v>0.55323107391025839</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>0.59872793140222458</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C38">
-        <v>0.63043219735719702</v>
+        <v>0.59778379949565807</v>
       </c>
       <c r="D38">
-        <v>0.6040349668891668</v>
+        <v>0.63002419279566801</v>
       </c>
       <c r="E38">
-        <v>0.62136367605138643</v>
+        <v>0.60685419974695398</v>
       </c>
       <c r="F38">
-        <v>0.61217914572441412</v>
+        <v>0.62311645092239809</v>
       </c>
       <c r="G38">
-        <v>0.59883520256950173</v>
+        <v>0.61267377675427925</v>
       </c>
       <c r="H38">
-        <v>0.57743907544465611</v>
+        <v>0.59546987257837047</v>
       </c>
       <c r="I38">
-        <v>0.59102347573513436</v>
+        <v>0.5772423943014261</v>
       </c>
       <c r="J38">
-        <v>0.59635107167024848</v>
+        <v>0.59138182004798967</v>
       </c>
       <c r="K38">
-        <v>0.61346201954201851</v>
+        <v>0.59620786457297548</v>
       </c>
       <c r="L38">
-        <v>0.60683116843606344</v>
+        <v>0.61720337884045873</v>
       </c>
       <c r="M38">
-        <v>0.59218142652272587</v>
+        <v>0.61525506693857868</v>
       </c>
       <c r="N38">
-        <v>0.565577782332361</v>
+        <v>0.60339358642229779</v>
       </c>
       <c r="O38">
-        <v>0.56830090311161718</v>
+        <v>0.57696410669805309</v>
       </c>
       <c r="P38">
-        <v>0.54358044152126106</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.5826177800160165</v>
+      </c>
+      <c r="Q38">
+        <v>0.5586109038089675</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B39">
-        <v>0.59744319302056059</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C39">
-        <v>0.62825055317865541</v>
+        <v>0.59709787952568993</v>
       </c>
       <c r="D39">
-        <v>0.60208584283756783</v>
+        <v>0.62917409650851586</v>
       </c>
       <c r="E39">
-        <v>0.619783515455819</v>
+        <v>0.6036321218976719</v>
       </c>
       <c r="F39">
-        <v>0.61076261034429946</v>
+        <v>0.62173835974805058</v>
       </c>
       <c r="G39">
-        <v>0.59590619410863188</v>
+        <v>0.61220237275232725</v>
       </c>
       <c r="H39">
-        <v>0.57586448245668376</v>
+        <v>0.59555913194032573</v>
       </c>
       <c r="I39">
-        <v>0.59141424438234191</v>
+        <v>0.57534411571208255</v>
       </c>
       <c r="J39">
-        <v>0.5943847958906161</v>
+        <v>0.58521895881151376</v>
       </c>
       <c r="K39">
-        <v>0.61447343071083738</v>
+        <v>0.58891654717005082</v>
       </c>
       <c r="L39">
-        <v>0.61181218648922275</v>
+        <v>0.61173803309595898</v>
       </c>
       <c r="M39">
-        <v>0.60181146925813489</v>
+        <v>0.60875777031551459</v>
       </c>
       <c r="N39">
-        <v>0.57469643218825472</v>
+        <v>0.59145348729508362</v>
       </c>
       <c r="O39">
-        <v>0.57927506623962932</v>
+        <v>0.56866419577082206</v>
       </c>
       <c r="P39">
-        <v>0.55765742538064544</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.57120000281111172</v>
+      </c>
+      <c r="Q39">
+        <v>0.54995024105853918</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>0.59955586466039112</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C40">
-        <v>0.6316426024190851</v>
+        <v>0.5984604500625712</v>
       </c>
       <c r="D40">
-        <v>0.60960190690634009</v>
+        <v>0.62954788851915855</v>
       </c>
       <c r="E40">
-        <v>0.62560154971626825</v>
+        <v>0.6006298891881573</v>
       </c>
       <c r="F40">
-        <v>0.61680107599096723</v>
+        <v>0.61928503950180236</v>
       </c>
       <c r="G40">
-        <v>0.60050500406848606</v>
+        <v>0.61028012092590644</v>
       </c>
       <c r="H40">
-        <v>0.58113510098019883</v>
+        <v>0.59524944770544219</v>
       </c>
       <c r="I40">
-        <v>0.59751143463341339</v>
+        <v>0.57852399427383516</v>
       </c>
       <c r="J40">
-        <v>0.5973444817511504</v>
+        <v>0.59183880316182058</v>
       </c>
       <c r="K40">
-        <v>0.61491485998326567</v>
+        <v>0.58951069568926751</v>
       </c>
       <c r="L40">
-        <v>0.60961237692363146</v>
+        <v>0.60778505597732613</v>
       </c>
       <c r="M40">
-        <v>0.60738401087522043</v>
+        <v>0.60760606762050373</v>
       </c>
       <c r="N40">
-        <v>0.58714959143431489</v>
+        <v>0.60281332444896185</v>
       </c>
       <c r="O40">
-        <v>0.58531899347633698</v>
+        <v>0.58384178659469332</v>
       </c>
       <c r="P40">
-        <v>0.56810248595153312</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.581663817291453</v>
+      </c>
+      <c r="Q40">
+        <v>0.56715342854466821</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B41">
-        <v>0.63090089983628916</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C41">
-        <v>0.63085900612598467</v>
+        <v>0.63095909201145284</v>
       </c>
       <c r="D41">
-        <v>0.62998298973547018</v>
+        <v>0.6311601953878897</v>
       </c>
       <c r="E41">
-        <v>0.62752924868445348</v>
+        <v>0.63097026773356113</v>
       </c>
       <c r="F41">
-        <v>0.59645487278609244</v>
+        <v>0.62813867866075845</v>
       </c>
       <c r="G41">
-        <v>0.56658047646546494</v>
+        <v>0.5980925580391544</v>
       </c>
       <c r="H41">
-        <v>0.58466348322583317</v>
+        <v>0.56811365763677268</v>
       </c>
       <c r="I41">
-        <v>0.57528344720654412</v>
+        <v>0.58516785291284645</v>
       </c>
       <c r="J41">
-        <v>0.56127337867267624</v>
+        <v>0.57283727650214855</v>
       </c>
       <c r="K41">
-        <v>0.52712624444353995</v>
+        <v>0.55620731672494794</v>
       </c>
       <c r="L41">
-        <v>0.4801376227899582</v>
+        <v>0.52388855216146091</v>
       </c>
       <c r="M41">
-        <v>0.42277244610889497</v>
+        <v>0.4804673709513026</v>
       </c>
       <c r="N41">
-        <v>0.33846818745298313</v>
+        <v>0.42106467971846728</v>
       </c>
       <c r="O41">
-        <v>0.28341306048216991</v>
+        <v>0.33064521089054061</v>
       </c>
       <c r="P41">
-        <v>0.2312723477053597</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.27420910205874671</v>
+      </c>
+      <c r="Q41">
+        <v>0.21685849769647761</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>0.62909024973643346</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C42">
-        <v>0.62857486341545155</v>
+        <v>0.62941068213827422</v>
       </c>
       <c r="D42">
-        <v>0.63142843574607521</v>
+        <v>0.63093798746665308</v>
       </c>
       <c r="E42">
-        <v>0.63276301720958505</v>
+        <v>0.63008378112164942</v>
       </c>
       <c r="F42">
-        <v>0.61917962223765133</v>
+        <v>0.63142098083200648</v>
       </c>
       <c r="G42">
-        <v>0.60465499948478041</v>
+        <v>0.61756136973862841</v>
       </c>
       <c r="H42">
-        <v>0.60090872156188968</v>
+        <v>0.60260298959499514</v>
       </c>
       <c r="I42">
-        <v>0.57348781042276242</v>
+        <v>0.60117350290805749</v>
       </c>
       <c r="J42">
-        <v>0.51354045225327838</v>
+        <v>0.56939639788795049</v>
       </c>
       <c r="K42">
-        <v>0.48635551288647239</v>
+        <v>0.5065684713916675</v>
       </c>
       <c r="L42">
-        <v>0.47649019695714973</v>
+        <v>0.47771696970755267</v>
       </c>
       <c r="M42">
-        <v>0.49911397989993411</v>
+        <v>0.46619744987379319</v>
       </c>
       <c r="N42">
-        <v>0.51505332594740105</v>
+        <v>0.48928779215128021</v>
       </c>
       <c r="O42">
-        <v>0.49364451248992758</v>
+        <v>0.50611169074027407</v>
       </c>
       <c r="P42">
-        <v>0.47644298694190551</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.48435579528328421</v>
+      </c>
+      <c r="Q42">
+        <v>0.46403039656409178</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B43">
-        <v>0.63122621095327303</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C43">
-        <v>0.63299934807675895</v>
+        <v>0.63076489532468683</v>
       </c>
       <c r="D43">
-        <v>0.63546984202314993</v>
+        <v>0.63310979185946059</v>
       </c>
       <c r="E43">
-        <v>0.63519192752762643</v>
+        <v>0.63403675403265247</v>
       </c>
       <c r="F43">
-        <v>0.62423656448332876</v>
+        <v>0.63335273740174092</v>
       </c>
       <c r="G43">
-        <v>0.61237976238839698</v>
+        <v>0.61943386853509641</v>
       </c>
       <c r="H43">
-        <v>0.62276659052666106</v>
+        <v>0.6067097752552727</v>
       </c>
       <c r="I43">
-        <v>0.60592910587255733</v>
+        <v>0.61831454348262649</v>
       </c>
       <c r="J43">
-        <v>0.53919479614498311</v>
+        <v>0.60011529042023126</v>
       </c>
       <c r="K43">
-        <v>0.52088892938250708</v>
+        <v>0.52974364047080758</v>
       </c>
       <c r="L43">
-        <v>0.50764958169995522</v>
+        <v>0.50914770188689684</v>
       </c>
       <c r="M43">
-        <v>0.5018937658300987</v>
+        <v>0.49280573907311459</v>
       </c>
       <c r="N43">
-        <v>0.50191905609895615</v>
+        <v>0.48975702817544492</v>
       </c>
       <c r="O43">
-        <v>0.49668178458835072</v>
+        <v>0.49340297154105378</v>
       </c>
       <c r="P43">
-        <v>0.4582307882533907</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.4927579003923071</v>
+      </c>
+      <c r="Q43">
+        <v>0.451057939842056</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B44">
-        <v>0.5934999120062443</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C44">
-        <v>0.58744221481961112</v>
+        <v>0.59325899855069353</v>
       </c>
       <c r="D44">
-        <v>0.57303834596765235</v>
+        <v>0.58849412289829073</v>
       </c>
       <c r="E44">
-        <v>0.60609297374771431</v>
+        <v>0.57414392504152001</v>
       </c>
       <c r="F44">
-        <v>0.62306887119190069</v>
+        <v>0.60827573219967945</v>
       </c>
       <c r="G44">
-        <v>0.59697561365989282</v>
+        <v>0.62254126762475248</v>
       </c>
       <c r="H44">
-        <v>0.56264561402026148</v>
+        <v>0.59897179646086574</v>
       </c>
       <c r="I44">
-        <v>0.53053790786060984</v>
+        <v>0.56501274076548702</v>
       </c>
       <c r="J44">
-        <v>0.50999251151015057</v>
+        <v>0.53116894971497552</v>
       </c>
       <c r="K44">
-        <v>0.48704855550532922</v>
+        <v>0.51132636348400184</v>
       </c>
       <c r="L44">
-        <v>0.44424713159083451</v>
+        <v>0.48930347965973903</v>
       </c>
       <c r="M44">
-        <v>0.37164967177694408</v>
+        <v>0.44700085027497261</v>
       </c>
       <c r="N44">
-        <v>0.27913266648860879</v>
+        <v>0.37205348209109879</v>
       </c>
       <c r="O44">
-        <v>0.181949892270932</v>
+        <v>0.27256788435465962</v>
       </c>
       <c r="P44">
-        <v>0.1351314804877318</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.1819863913083494</v>
+      </c>
+      <c r="Q44">
+        <v>0.13345827977673269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B45">
-        <v>0.58410706858244421</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C45">
-        <v>0.61033361805941944</v>
+        <v>0.58468366840865194</v>
       </c>
       <c r="D45">
-        <v>0.55283848972104799</v>
+        <v>0.60874211222325258</v>
       </c>
       <c r="E45">
-        <v>0.54576136583019086</v>
+        <v>0.54974116117137939</v>
       </c>
       <c r="F45">
-        <v>0.5542054759359446</v>
+        <v>0.542817136041433</v>
       </c>
       <c r="G45">
-        <v>0.5059580126599561</v>
+        <v>0.55615817327951922</v>
       </c>
       <c r="H45">
-        <v>0.49094004936414237</v>
+        <v>0.51457762689789732</v>
       </c>
       <c r="I45">
-        <v>0.48202712461511199</v>
+        <v>0.50198239154211344</v>
       </c>
       <c r="J45">
-        <v>0.45498680120974577</v>
+        <v>0.48943624740074992</v>
       </c>
       <c r="K45">
-        <v>0.42372774795111029</v>
+        <v>0.46216412794067008</v>
       </c>
       <c r="L45">
-        <v>0.36803003262332301</v>
+        <v>0.43267348668222838</v>
       </c>
       <c r="M45">
-        <v>0.27332798860152052</v>
+        <v>0.37852505656101298</v>
       </c>
       <c r="N45">
-        <v>0.23653563441380249</v>
+        <v>0.28717935465056033</v>
       </c>
       <c r="O45">
-        <v>0.199015783055948</v>
+        <v>0.24965319538173289</v>
       </c>
       <c r="P45">
-        <v>0.1692235536596263</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.20725217770185311</v>
+      </c>
+      <c r="Q45">
+        <v>0.1771522340315578</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B46">
-        <v>0.46180172080334209</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C46">
-        <v>0.60839066547642695</v>
+        <v>0.46265314815284631</v>
       </c>
       <c r="D46">
-        <v>0.56864371341658781</v>
+        <v>0.6092480042851921</v>
       </c>
       <c r="E46">
-        <v>0.51605902608165133</v>
+        <v>0.57071591275812572</v>
       </c>
       <c r="F46">
-        <v>0.5390029261457584</v>
+        <v>0.51732414397676418</v>
       </c>
       <c r="G46">
-        <v>0.55816087776751366</v>
+        <v>0.53657585498332905</v>
       </c>
       <c r="H46">
-        <v>0.53934388202285766</v>
+        <v>0.5579864375732424</v>
       </c>
       <c r="I46">
-        <v>0.4765679512907795</v>
+        <v>0.53969142646589352</v>
       </c>
       <c r="J46">
-        <v>0.40357062543508643</v>
+        <v>0.47404415321461879</v>
       </c>
       <c r="K46">
-        <v>0.35552711322670022</v>
+        <v>0.40791116391446658</v>
       </c>
       <c r="L46">
-        <v>0.31152026914909009</v>
+        <v>0.36035476712637893</v>
       </c>
       <c r="M46">
-        <v>0.28632504205622089</v>
+        <v>0.31394791955197848</v>
       </c>
       <c r="N46">
-        <v>0.25632977957039038</v>
+        <v>0.2916754266913007</v>
       </c>
       <c r="O46">
-        <v>0.20674417617403079</v>
+        <v>0.26688077092210449</v>
       </c>
       <c r="P46">
-        <v>0.15354053154265829</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.21931373216701419</v>
+      </c>
+      <c r="Q46">
+        <v>0.17162075574256919</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B47">
-        <v>0.6134229955861823</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C47">
-        <v>0.5999379637382366</v>
+        <v>0.6122877017098638</v>
       </c>
       <c r="D47">
-        <v>0.5865062498398429</v>
+        <v>0.59707692788207178</v>
       </c>
       <c r="E47">
-        <v>0.59399788992651481</v>
+        <v>0.58420854393597055</v>
       </c>
       <c r="F47">
-        <v>0.55161311500042409</v>
+        <v>0.59317317636165734</v>
       </c>
       <c r="G47">
-        <v>0.54446633358046093</v>
+        <v>0.55361858960226629</v>
       </c>
       <c r="H47">
-        <v>0.52229746551887724</v>
+        <v>0.54827386430168734</v>
       </c>
       <c r="I47">
-        <v>0.5027697034422608</v>
+        <v>0.52567979787140906</v>
       </c>
       <c r="J47">
-        <v>0.46376807132368819</v>
+        <v>0.50328705139206964</v>
       </c>
       <c r="K47">
-        <v>0.40915663105559602</v>
+        <v>0.4653837029337668</v>
       </c>
       <c r="L47">
-        <v>0.34479275195671699</v>
+        <v>0.4080542010766357</v>
       </c>
       <c r="M47">
-        <v>0.29809938588363932</v>
+        <v>0.34406990088173423</v>
       </c>
       <c r="N47">
-        <v>0.28135377624453528</v>
+        <v>0.29883210237581231</v>
       </c>
       <c r="O47">
-        <v>0.28072705643064988</v>
+        <v>0.28040995667370971</v>
       </c>
       <c r="P47">
-        <v>0.26272305581704858</v>
+        <v>0.27698846487236478</v>
+      </c>
+      <c r="Q47">
+        <v>0.25814640029049712</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P16 B18:P47 B17:F17 H17:P17">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="B2:Q47">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2972,7 +3072,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_ADJR2.xlsx
@@ -1,220 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\X13.cis.beta.carotene\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV0_ADJR2</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,19 +63,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -316,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -348,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -383,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -559,2520 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="14" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>0.39815189499627168</v>
+        <v>0.398603495011786</v>
       </c>
       <c r="D2">
-        <v>0.57787455393980247</v>
+        <v>0.5796215309538708</v>
       </c>
       <c r="E2">
-        <v>0.61176472064984433</v>
+        <v>0.6115443543940347</v>
       </c>
       <c r="F2">
-        <v>0.62463140683688834</v>
+        <v>0.6229120939490871</v>
       </c>
       <c r="G2">
-        <v>0.6111233904392831</v>
+        <v>0.6094901072200055</v>
       </c>
       <c r="H2">
-        <v>0.6359304564778907</v>
+        <v>0.6333952788413868</v>
       </c>
       <c r="I2">
-        <v>0.64149044279366652</v>
+        <v>0.6378565372190187</v>
       </c>
       <c r="J2">
-        <v>0.61841269666002674</v>
+        <v>0.616711841009653</v>
       </c>
       <c r="K2">
-        <v>0.63320109248164513</v>
+        <v>0.6269624440033628</v>
       </c>
       <c r="L2">
-        <v>0.6147839562587486</v>
+        <v>0.6077367071259279</v>
       </c>
       <c r="M2">
-        <v>0.60253043810342277</v>
+        <v>0.5965602976620978</v>
       </c>
       <c r="N2">
-        <v>0.56194516669014827</v>
+        <v>0.5512259691986484</v>
       </c>
       <c r="O2">
-        <v>0.49893119971929739</v>
+        <v>0.4899418299502862</v>
       </c>
       <c r="P2">
-        <v>0.45075554028388648</v>
+        <v>0.4346285606088682</v>
       </c>
       <c r="Q2">
-        <v>0.42095131686386272</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>0.4090620257545803</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>0.4620080546524713</v>
+        <v>0.4617014151424073</v>
       </c>
       <c r="D3">
-        <v>0.5955512898292521</v>
+        <v>0.5970153335015437</v>
       </c>
       <c r="E3">
-        <v>0.58341388428132868</v>
+        <v>0.5847151295184726</v>
       </c>
       <c r="F3">
-        <v>0.54340105501470759</v>
+        <v>0.5414156004513765</v>
       </c>
       <c r="G3">
-        <v>0.57275739904981848</v>
+        <v>0.57218006600289</v>
       </c>
       <c r="H3">
-        <v>0.57583367625568382</v>
+        <v>0.572126667696974</v>
       </c>
       <c r="I3">
-        <v>0.52723528631210392</v>
+        <v>0.5283849928401205</v>
       </c>
       <c r="J3">
-        <v>0.51427893723594487</v>
+        <v>0.5110956021363765</v>
       </c>
       <c r="K3">
-        <v>0.46599067167480102</v>
+        <v>0.463247882323941</v>
       </c>
       <c r="L3">
-        <v>0.4455050363247377</v>
+        <v>0.4444102361469563</v>
       </c>
       <c r="M3">
-        <v>0.4212638893461268</v>
+        <v>0.4180254343813385</v>
       </c>
       <c r="N3">
-        <v>0.37706437297776502</v>
+        <v>0.3746319375996299</v>
       </c>
       <c r="O3">
-        <v>0.34274170001672177</v>
+        <v>0.3437547289082166</v>
       </c>
       <c r="P3">
-        <v>0.34229048093532888</v>
+        <v>0.3424860092376946</v>
       </c>
       <c r="Q3">
-        <v>0.35805029830346269</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>0.3607250247618591</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>0.42094741306103189</v>
+        <v>0.4215462238471482</v>
       </c>
       <c r="D4">
-        <v>0.5671615771206836</v>
+        <v>0.5676225425423789</v>
       </c>
       <c r="E4">
-        <v>0.57602670353349517</v>
+        <v>0.5775584725828261</v>
       </c>
       <c r="F4">
-        <v>0.58676545092628518</v>
+        <v>0.5893636719574695</v>
       </c>
       <c r="G4">
-        <v>0.59511389560741457</v>
+        <v>0.6000055092807184</v>
       </c>
       <c r="H4">
-        <v>0.63641865726913838</v>
+        <v>0.6365759437988273</v>
       </c>
       <c r="I4">
-        <v>0.63885407739461486</v>
+        <v>0.639163927112923</v>
       </c>
       <c r="J4">
-        <v>0.62680484220873278</v>
+        <v>0.628610880181693</v>
       </c>
       <c r="K4">
-        <v>0.60679232006620376</v>
+        <v>0.6099327624240019</v>
       </c>
       <c r="L4">
-        <v>0.57650683501590083</v>
+        <v>0.5843241548221342</v>
       </c>
       <c r="M4">
-        <v>0.54353857515041204</v>
+        <v>0.5539149419763322</v>
       </c>
       <c r="N4">
-        <v>0.48617071797042138</v>
+        <v>0.4964997287565815</v>
       </c>
       <c r="O4">
-        <v>0.43496642624865289</v>
+        <v>0.4472110040074704</v>
       </c>
       <c r="P4">
-        <v>0.39869383938894309</v>
+        <v>0.4120940745849033</v>
       </c>
       <c r="Q4">
-        <v>0.36880905378071732</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>0.3770516311751237</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>0.58848210272375623</v>
+        <v>0.5905294755624082</v>
       </c>
       <c r="D5">
-        <v>0.59537719904355635</v>
+        <v>0.5981915554202726</v>
       </c>
       <c r="E5">
-        <v>0.60260907327611279</v>
+        <v>0.6045045790507451</v>
       </c>
       <c r="F5">
-        <v>0.59693460208020732</v>
+        <v>0.6006516118084487</v>
       </c>
       <c r="G5">
-        <v>0.60447150262537352</v>
+        <v>0.6086788934441667</v>
       </c>
       <c r="H5">
-        <v>0.60265773515026766</v>
+        <v>0.606776384219445</v>
       </c>
       <c r="I5">
-        <v>0.58572709370297815</v>
+        <v>0.5890617907226202</v>
       </c>
       <c r="J5">
-        <v>0.54555270874502837</v>
+        <v>0.5459926364876917</v>
       </c>
       <c r="K5">
-        <v>0.47163604316932622</v>
+        <v>0.4739255027035414</v>
       </c>
       <c r="L5">
-        <v>0.4329583363011611</v>
+        <v>0.4352985341614405</v>
       </c>
       <c r="M5">
-        <v>0.40130554676409957</v>
+        <v>0.4015295240755037</v>
       </c>
       <c r="N5">
-        <v>0.39923194943718882</v>
+        <v>0.3972988994666473</v>
       </c>
       <c r="O5">
-        <v>0.40524570420345241</v>
+        <v>0.4040897795225095</v>
       </c>
       <c r="P5">
-        <v>0.40387401333989098</v>
+        <v>0.4064016711740003</v>
       </c>
       <c r="Q5">
-        <v>0.39808635137944542</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>0.404993325409037</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>0.58700105037331329</v>
+        <v>0.5864256049358012</v>
       </c>
       <c r="D6">
-        <v>0.5939857513291249</v>
+        <v>0.5935788908407292</v>
       </c>
       <c r="E6">
-        <v>0.6051034332421813</v>
+        <v>0.6039908631011724</v>
       </c>
       <c r="F6">
-        <v>0.61031416994237764</v>
+        <v>0.6089097911532259</v>
       </c>
       <c r="G6">
-        <v>0.6309672218931901</v>
+        <v>0.6290467009621706</v>
       </c>
       <c r="H6">
-        <v>0.62353375694852531</v>
+        <v>0.6225151607013525</v>
       </c>
       <c r="I6">
-        <v>0.59759302988529706</v>
+        <v>0.5957963809010661</v>
       </c>
       <c r="J6">
-        <v>0.57248611455445464</v>
+        <v>0.5693968990328666</v>
       </c>
       <c r="K6">
-        <v>0.53929703663291828</v>
+        <v>0.5385332064928584</v>
       </c>
       <c r="L6">
-        <v>0.52358917515587033</v>
+        <v>0.5214438396402963</v>
       </c>
       <c r="M6">
-        <v>0.49427514047767113</v>
+        <v>0.489361132552652</v>
       </c>
       <c r="N6">
-        <v>0.47590498622381128</v>
+        <v>0.4703783425760318</v>
       </c>
       <c r="O6">
-        <v>0.45376615529974929</v>
+        <v>0.4534980653519925</v>
       </c>
       <c r="P6">
-        <v>0.44747193975219729</v>
+        <v>0.4496461070298668</v>
       </c>
       <c r="Q6">
-        <v>0.43930241553975152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>0.4374177385588689</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>0.42690265688449891</v>
+        <v>0.4237376363433553</v>
       </c>
       <c r="D7">
-        <v>0.5813186378298314</v>
+        <v>0.5797804709016181</v>
       </c>
       <c r="E7">
-        <v>0.63021196348481923</v>
+        <v>0.6290760928983262</v>
       </c>
       <c r="F7">
-        <v>0.63922997146562954</v>
+        <v>0.6372842679356893</v>
       </c>
       <c r="G7">
-        <v>0.63780505740827587</v>
+        <v>0.6379197970331528</v>
       </c>
       <c r="H7">
-        <v>0.64876984802161475</v>
+        <v>0.646987070811315</v>
       </c>
       <c r="I7">
-        <v>0.63370293920201071</v>
+        <v>0.6374658916424079</v>
       </c>
       <c r="J7">
-        <v>0.63512334494500311</v>
+        <v>0.6387656202158222</v>
       </c>
       <c r="K7">
-        <v>0.62371305045799985</v>
+        <v>0.6231026941488707</v>
       </c>
       <c r="L7">
-        <v>0.5977849326005068</v>
+        <v>0.5992399548957057</v>
       </c>
       <c r="M7">
-        <v>0.56988072249955513</v>
+        <v>0.5741213981328667</v>
       </c>
       <c r="N7">
-        <v>0.50479567082936372</v>
+        <v>0.5151055361695721</v>
       </c>
       <c r="O7">
-        <v>0.46175203592725661</v>
+        <v>0.4702886143887231</v>
       </c>
       <c r="P7">
-        <v>0.4139031763988601</v>
+        <v>0.4206097948044066</v>
       </c>
       <c r="Q7">
-        <v>0.37751469823517447</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>0.3914791201438557</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>0.49953262606958287</v>
+        <v>0.4993576157248136</v>
       </c>
       <c r="D8">
-        <v>0.57600903686765126</v>
+        <v>0.5764728033376713</v>
       </c>
       <c r="E8">
-        <v>0.62732854345088462</v>
+        <v>0.6270923041613999</v>
       </c>
       <c r="F8">
-        <v>0.64039357418131304</v>
+        <v>0.638617316013244</v>
       </c>
       <c r="G8">
-        <v>0.64686235120286417</v>
+        <v>0.6459393664686576</v>
       </c>
       <c r="H8">
-        <v>0.63651765860438558</v>
+        <v>0.6293847729504991</v>
       </c>
       <c r="I8">
-        <v>0.63447392962171201</v>
+        <v>0.6278343407291129</v>
       </c>
       <c r="J8">
-        <v>0.60734448034278232</v>
+        <v>0.5981098229093306</v>
       </c>
       <c r="K8">
-        <v>0.56546192398174588</v>
+        <v>0.5531791167532928</v>
       </c>
       <c r="L8">
-        <v>0.54320336430408711</v>
+        <v>0.529599213432713</v>
       </c>
       <c r="M8">
-        <v>0.52180283819461615</v>
+        <v>0.5108858541575627</v>
       </c>
       <c r="N8">
-        <v>0.48625369832544191</v>
+        <v>0.473168630552142</v>
       </c>
       <c r="O8">
-        <v>0.42036149027107422</v>
+        <v>0.4061224310702001</v>
       </c>
       <c r="P8">
-        <v>0.37164421021123212</v>
+        <v>0.3565150070749667</v>
       </c>
       <c r="Q8">
-        <v>0.33808195211895681</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>0.3256260343490119</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>0.49938038624550168</v>
+        <v>0.4980348066975618</v>
       </c>
       <c r="D9">
-        <v>0.57649620843067273</v>
+        <v>0.5740107050761313</v>
       </c>
       <c r="E9">
-        <v>0.62667936242333311</v>
+        <v>0.6248304379267619</v>
       </c>
       <c r="F9">
-        <v>0.63981319155476424</v>
+        <v>0.6384518745722876</v>
       </c>
       <c r="G9">
-        <v>0.64769707440644864</v>
+        <v>0.6491209975360522</v>
       </c>
       <c r="H9">
-        <v>0.63630950433631683</v>
+        <v>0.6371793320637918</v>
       </c>
       <c r="I9">
-        <v>0.63829929034859001</v>
+        <v>0.6392130233742884</v>
       </c>
       <c r="J9">
-        <v>0.63086184330794837</v>
+        <v>0.6312315995968165</v>
       </c>
       <c r="K9">
-        <v>0.60962110079977394</v>
+        <v>0.6097434587923387</v>
       </c>
       <c r="L9">
-        <v>0.60051910657040053</v>
+        <v>0.5959070036561815</v>
       </c>
       <c r="M9">
-        <v>0.59988667290925946</v>
+        <v>0.5950464422264008</v>
       </c>
       <c r="N9">
-        <v>0.59047245817070204</v>
+        <v>0.583671124713479</v>
       </c>
       <c r="O9">
-        <v>0.55897035888363911</v>
+        <v>0.5530975582934453</v>
       </c>
       <c r="P9">
-        <v>0.5431045571497386</v>
+        <v>0.5354491004594927</v>
       </c>
       <c r="Q9">
-        <v>0.52343760857770094</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>0.5168898758492021</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>0.49990240040785289</v>
+        <v>0.5001438566609585</v>
       </c>
       <c r="D10">
-        <v>0.57726167486777236</v>
+        <v>0.575747383557518</v>
       </c>
       <c r="E10">
-        <v>0.62794504060163814</v>
+        <v>0.626030842429744</v>
       </c>
       <c r="F10">
-        <v>0.6421462048051485</v>
+        <v>0.639675277225833</v>
       </c>
       <c r="G10">
-        <v>0.65222971539842822</v>
+        <v>0.6480397015468361</v>
       </c>
       <c r="H10">
-        <v>0.64073812103338934</v>
+        <v>0.636163030522737</v>
       </c>
       <c r="I10">
-        <v>0.6432897635854401</v>
+        <v>0.6390889266304092</v>
       </c>
       <c r="J10">
-        <v>0.6365296250071264</v>
+        <v>0.6321072653537733</v>
       </c>
       <c r="K10">
-        <v>0.62029159228443331</v>
+        <v>0.6129545079381332</v>
       </c>
       <c r="L10">
-        <v>0.60798901763432467</v>
+        <v>0.6003636467020448</v>
       </c>
       <c r="M10">
-        <v>0.60601912346763542</v>
+        <v>0.599798906868797</v>
       </c>
       <c r="N10">
-        <v>0.59560051661658109</v>
+        <v>0.5889343190354048</v>
       </c>
       <c r="O10">
-        <v>0.56437210452920072</v>
+        <v>0.557233885964135</v>
       </c>
       <c r="P10">
-        <v>0.54591199225214115</v>
+        <v>0.5363409841546602</v>
       </c>
       <c r="Q10">
-        <v>0.52046816921103523</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>0.5117445250486772</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>0.49861283361294267</v>
+        <v>0.499725909870483</v>
       </c>
       <c r="D11">
-        <v>0.57536031216446815</v>
+        <v>0.5779786783326801</v>
       </c>
       <c r="E11">
-        <v>0.6271815643116212</v>
+        <v>0.6284199037103522</v>
       </c>
       <c r="F11">
-        <v>0.63971879794023256</v>
+        <v>0.6404968937853383</v>
       </c>
       <c r="G11">
-        <v>0.64739583443646354</v>
+        <v>0.6496560102291485</v>
       </c>
       <c r="H11">
-        <v>0.63800464036618421</v>
+        <v>0.6386965139368095</v>
       </c>
       <c r="I11">
-        <v>0.63834810185657098</v>
+        <v>0.6402215298307551</v>
       </c>
       <c r="J11">
-        <v>0.63003734600639505</v>
+        <v>0.6351517944607956</v>
       </c>
       <c r="K11">
-        <v>0.61194500366852633</v>
+        <v>0.6171994075087799</v>
       </c>
       <c r="L11">
-        <v>0.60855139344580578</v>
+        <v>0.6131980569778731</v>
       </c>
       <c r="M11">
-        <v>0.6122295327549514</v>
+        <v>0.6138146104506439</v>
       </c>
       <c r="N11">
-        <v>0.60308304878303598</v>
+        <v>0.6062125044734721</v>
       </c>
       <c r="O11">
-        <v>0.57178092533128189</v>
+        <v>0.5758767856855294</v>
       </c>
       <c r="P11">
-        <v>0.548598608210353</v>
+        <v>0.5528038039065752</v>
       </c>
       <c r="Q11">
-        <v>0.53146491711541965</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>0.5379160002596108</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>0.60578222902900691</v>
+        <v>0.6051000095029837</v>
       </c>
       <c r="D12">
-        <v>0.61575804244160359</v>
+        <v>0.6151827290492567</v>
       </c>
       <c r="E12">
-        <v>0.6227675264027992</v>
+        <v>0.6230081594335577</v>
       </c>
       <c r="F12">
-        <v>0.6229822456599462</v>
+        <v>0.6236784946416618</v>
       </c>
       <c r="G12">
-        <v>0.62732839340811952</v>
+        <v>0.6261728412999161</v>
       </c>
       <c r="H12">
-        <v>0.62508433739440794</v>
+        <v>0.6258876930353688</v>
       </c>
       <c r="I12">
-        <v>0.60433823786416285</v>
+        <v>0.6052111361851702</v>
       </c>
       <c r="J12">
-        <v>0.56302119761757541</v>
+        <v>0.5639306619255363</v>
       </c>
       <c r="K12">
-        <v>0.50065472070546013</v>
+        <v>0.4993405266870967</v>
       </c>
       <c r="L12">
-        <v>0.44578416849707247</v>
+        <v>0.4400226248618244</v>
       </c>
       <c r="M12">
-        <v>0.38101662923790158</v>
+        <v>0.3719134458837232</v>
       </c>
       <c r="N12">
-        <v>0.35437506661373253</v>
+        <v>0.3456553183868946</v>
       </c>
       <c r="O12">
-        <v>0.36016943683795483</v>
+        <v>0.3531473134071786</v>
       </c>
       <c r="P12">
-        <v>0.3611549922842564</v>
+        <v>0.3590936518852654</v>
       </c>
       <c r="Q12">
-        <v>0.33681355636569887</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>0.3345172527736233</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.60202791349036266</v>
+        <v>0.6017763648084599</v>
       </c>
       <c r="D13">
-        <v>0.59986763428894863</v>
+        <v>0.598325304619442</v>
       </c>
       <c r="E13">
-        <v>0.6099706508058822</v>
+        <v>0.6107006601181375</v>
       </c>
       <c r="F13">
-        <v>0.62452961867005019</v>
+        <v>0.6217152221872957</v>
       </c>
       <c r="G13">
-        <v>0.58020739928380161</v>
+        <v>0.5817592587248596</v>
       </c>
       <c r="H13">
-        <v>0.56478879705651597</v>
+        <v>0.5622567425245549</v>
       </c>
       <c r="I13">
-        <v>0.56149673545954659</v>
+        <v>0.5613888640055945</v>
       </c>
       <c r="J13">
-        <v>0.5471126001382548</v>
+        <v>0.5476272051399351</v>
       </c>
       <c r="K13">
-        <v>0.4759316001874187</v>
+        <v>0.4753227471852248</v>
       </c>
       <c r="L13">
-        <v>0.40789735688664391</v>
+        <v>0.4093760998991058</v>
       </c>
       <c r="M13">
-        <v>0.38631202286234079</v>
+        <v>0.385895625438136</v>
       </c>
       <c r="N13">
-        <v>0.3798120180479006</v>
+        <v>0.3846510861913531</v>
       </c>
       <c r="O13">
-        <v>0.35778237852331068</v>
+        <v>0.3617976302076865</v>
       </c>
       <c r="P13">
-        <v>0.34842964795712161</v>
+        <v>0.3560396188236627</v>
       </c>
       <c r="Q13">
-        <v>0.31386195043541559</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>0.3218966079262589</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>0.42703763049190818</v>
+        <v>0.4259866773691758</v>
       </c>
       <c r="D14">
-        <v>0.580047613993387</v>
+        <v>0.5788855496486157</v>
       </c>
       <c r="E14">
-        <v>0.62984990539810637</v>
+        <v>0.6265842503391412</v>
       </c>
       <c r="F14">
-        <v>0.63963018393112137</v>
+        <v>0.6363031620127618</v>
       </c>
       <c r="G14">
-        <v>0.64035501515982474</v>
+        <v>0.637168258726418</v>
       </c>
       <c r="H14">
-        <v>0.64696396969807946</v>
+        <v>0.6513511554313515</v>
       </c>
       <c r="I14">
-        <v>0.64010653175241039</v>
+        <v>0.6395466321422894</v>
       </c>
       <c r="J14">
-        <v>0.64320779705355302</v>
+        <v>0.6432820255965533</v>
       </c>
       <c r="K14">
-        <v>0.63917247783765807</v>
+        <v>0.6384006947307795</v>
       </c>
       <c r="L14">
-        <v>0.62607399782060513</v>
+        <v>0.6250744182237202</v>
       </c>
       <c r="M14">
-        <v>0.62163879793413857</v>
+        <v>0.6214878063881102</v>
       </c>
       <c r="N14">
-        <v>0.60245302034147352</v>
+        <v>0.5966179309399365</v>
       </c>
       <c r="O14">
-        <v>0.57685031742033888</v>
+        <v>0.5686812365904859</v>
       </c>
       <c r="P14">
-        <v>0.53722974872217533</v>
+        <v>0.5307024975454619</v>
       </c>
       <c r="Q14">
-        <v>0.49287151463582068</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>0.4817706674435866</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>0.42605504838103059</v>
+        <v>0.426582304168972</v>
       </c>
       <c r="D15">
-        <v>0.58021368030159892</v>
+        <v>0.5806889119271192</v>
       </c>
       <c r="E15">
-        <v>0.62995230366868538</v>
+        <v>0.628141816395726</v>
       </c>
       <c r="F15">
-        <v>0.63852435648371064</v>
+        <v>0.6363369524474436</v>
       </c>
       <c r="G15">
-        <v>0.6386506036606292</v>
+        <v>0.6378467126661298</v>
       </c>
       <c r="H15">
-        <v>0.65106966560787927</v>
+        <v>0.6458420352814049</v>
       </c>
       <c r="I15">
-        <v>0.64220276479517835</v>
+        <v>0.6395098093529729</v>
       </c>
       <c r="J15">
-        <v>0.64609623401598804</v>
+        <v>0.6444741665038215</v>
       </c>
       <c r="K15">
-        <v>0.6414318142539237</v>
+        <v>0.6455478638604474</v>
       </c>
       <c r="L15">
-        <v>0.62976739415489735</v>
+        <v>0.6306475204323497</v>
       </c>
       <c r="M15">
-        <v>0.6259454348635255</v>
+        <v>0.6261437395520019</v>
       </c>
       <c r="N15">
-        <v>0.60341401779735238</v>
+        <v>0.6036634207492984</v>
       </c>
       <c r="O15">
-        <v>0.57227178058265649</v>
+        <v>0.5703108351178851</v>
       </c>
       <c r="P15">
-        <v>0.54830718287662672</v>
+        <v>0.5479881281384356</v>
       </c>
       <c r="Q15">
-        <v>0.53176276977478054</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>0.5335676259700074</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>0.42730276212907509</v>
+        <v>0.428316045949979</v>
       </c>
       <c r="D16">
-        <v>0.58081994904212764</v>
+        <v>0.5813165641942674</v>
       </c>
       <c r="E16">
-        <v>0.62877803106564667</v>
+        <v>0.6303489025766604</v>
       </c>
       <c r="F16">
-        <v>0.63751371341429386</v>
+        <v>0.6391117153933984</v>
       </c>
       <c r="G16">
-        <v>0.63677206340452064</v>
+        <v>0.6401182669737909</v>
       </c>
       <c r="H16">
-        <v>0.64836851336877976</v>
+        <v>0.6522391825315378</v>
       </c>
       <c r="I16">
-        <v>0.63993300151179011</v>
+        <v>0.6416777042578031</v>
       </c>
       <c r="J16">
-        <v>0.64464819685302055</v>
+        <v>0.6443647177612216</v>
       </c>
       <c r="K16">
-        <v>0.64150774360560858</v>
+        <v>0.6398027348383444</v>
       </c>
       <c r="L16">
-        <v>0.62926976910791699</v>
+        <v>0.6273511222868448</v>
       </c>
       <c r="M16">
-        <v>0.62388104724725135</v>
+        <v>0.623190331150643</v>
       </c>
       <c r="N16">
-        <v>0.59382836754672153</v>
+        <v>0.591504181022092</v>
       </c>
       <c r="O16">
-        <v>0.55473173887721139</v>
+        <v>0.5516242912197713</v>
       </c>
       <c r="P16">
-        <v>0.52661018346158439</v>
+        <v>0.5223385003622713</v>
       </c>
       <c r="Q16">
-        <v>0.51754139883036154</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>0.5113977505331011</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>0.42601904477445718</v>
+        <v>0.425414093594182</v>
       </c>
       <c r="D17">
-        <v>0.5788472021576665</v>
+        <v>0.5799663772002934</v>
       </c>
       <c r="E17">
-        <v>0.62597738440651252</v>
+        <v>0.6284166136780801</v>
       </c>
       <c r="F17">
-        <v>0.63427604883990107</v>
+        <v>0.6374476312687694</v>
       </c>
       <c r="G17">
-        <v>0.63344232907960418</v>
+        <v>0.6386483778135</v>
       </c>
       <c r="H17">
-        <v>0.64658076432822553</v>
+        <v>0.6489561298372426</v>
       </c>
       <c r="I17">
-        <v>0.63687332868466051</v>
+        <v>0.6431639786747028</v>
       </c>
       <c r="J17">
-        <v>0.64207403660381968</v>
+        <v>0.6465567794211955</v>
       </c>
       <c r="K17">
-        <v>0.63940071791959796</v>
+        <v>0.6423666945935415</v>
       </c>
       <c r="L17">
-        <v>0.62672857244039848</v>
+        <v>0.6315985783848117</v>
       </c>
       <c r="M17">
-        <v>0.62546340742474016</v>
+        <v>0.6284865556975443</v>
       </c>
       <c r="N17">
-        <v>0.59220389466037893</v>
+        <v>0.5980455456995405</v>
       </c>
       <c r="O17">
-        <v>0.55737170641110045</v>
+        <v>0.5632134588008192</v>
       </c>
       <c r="P17">
-        <v>0.52702860958912368</v>
+        <v>0.5307725051788302</v>
       </c>
       <c r="Q17">
-        <v>0.51897332051095035</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>0.5239530228168146</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.60489862142506601</v>
+        <v>0.6048280275615323</v>
       </c>
       <c r="D18">
-        <v>0.61367211497714302</v>
+        <v>0.6132125453901094</v>
       </c>
       <c r="E18">
-        <v>0.61696818843617385</v>
+        <v>0.6174224091509803</v>
       </c>
       <c r="F18">
-        <v>0.6121619869315863</v>
+        <v>0.6141245868084009</v>
       </c>
       <c r="G18">
-        <v>0.62516233754339734</v>
+        <v>0.6254506645065848</v>
       </c>
       <c r="H18">
-        <v>0.60893024514084371</v>
+        <v>0.6112325596599963</v>
       </c>
       <c r="I18">
-        <v>0.59857439546197633</v>
+        <v>0.5990669656960811</v>
       </c>
       <c r="J18">
-        <v>0.56359843504509144</v>
+        <v>0.5638008815597547</v>
       </c>
       <c r="K18">
-        <v>0.50700801102855475</v>
+        <v>0.5085604627778048</v>
       </c>
       <c r="L18">
-        <v>0.45272863895289989</v>
+        <v>0.4528816169458693</v>
       </c>
       <c r="M18">
-        <v>0.40456249023591973</v>
+        <v>0.4036717779086803</v>
       </c>
       <c r="N18">
-        <v>0.38538258748334009</v>
+        <v>0.3803605297511429</v>
       </c>
       <c r="O18">
-        <v>0.38540808811797622</v>
+        <v>0.3829515780051978</v>
       </c>
       <c r="P18">
-        <v>0.38996377743815402</v>
+        <v>0.3856053403727036</v>
       </c>
       <c r="Q18">
-        <v>0.39314173975792038</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>0.3876453328147946</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.60310769773121375</v>
+        <v>0.6035260226801238</v>
       </c>
       <c r="D19">
-        <v>0.61270776676430927</v>
+        <v>0.6125445767937102</v>
       </c>
       <c r="E19">
-        <v>0.6245144485342744</v>
+        <v>0.6251954338299706</v>
       </c>
       <c r="F19">
-        <v>0.63236218042075609</v>
+        <v>0.631793468497566</v>
       </c>
       <c r="G19">
-        <v>0.64871227847095869</v>
+        <v>0.6490901607129477</v>
       </c>
       <c r="H19">
-        <v>0.6259045337923751</v>
+        <v>0.6256713141672268</v>
       </c>
       <c r="I19">
-        <v>0.62497694504954115</v>
+        <v>0.6248825765472829</v>
       </c>
       <c r="J19">
-        <v>0.60113477610301147</v>
+        <v>0.597833241393123</v>
       </c>
       <c r="K19">
-        <v>0.56709493374360642</v>
+        <v>0.5674346315954505</v>
       </c>
       <c r="L19">
-        <v>0.53011852604366982</v>
+        <v>0.5300060466212377</v>
       </c>
       <c r="M19">
-        <v>0.49300182663685549</v>
+        <v>0.4939871825334476</v>
       </c>
       <c r="N19">
-        <v>0.46903041681538371</v>
+        <v>0.4722500957525277</v>
       </c>
       <c r="O19">
-        <v>0.44424874766177508</v>
+        <v>0.4490855669258114</v>
       </c>
       <c r="P19">
-        <v>0.43140770900454822</v>
+        <v>0.438766961381643</v>
       </c>
       <c r="Q19">
-        <v>0.4159662574872327</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>0.4200046458487685</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.60196001977856539</v>
+        <v>0.6027578627871766</v>
       </c>
       <c r="D20">
-        <v>0.61581922173616277</v>
+        <v>0.6180968301972832</v>
       </c>
       <c r="E20">
-        <v>0.63627585581383128</v>
+        <v>0.6363694576856784</v>
       </c>
       <c r="F20">
-        <v>0.63887343100844041</v>
+        <v>0.6384660344500601</v>
       </c>
       <c r="G20">
-        <v>0.65019163308977634</v>
+        <v>0.6499411537076493</v>
       </c>
       <c r="H20">
-        <v>0.65083937302508998</v>
+        <v>0.6500919321258721</v>
       </c>
       <c r="I20">
-        <v>0.63561040026972804</v>
+        <v>0.6344770703052395</v>
       </c>
       <c r="J20">
-        <v>0.60636209626617821</v>
+        <v>0.604108092770223</v>
       </c>
       <c r="K20">
-        <v>0.58275101427765275</v>
+        <v>0.5813513405686792</v>
       </c>
       <c r="L20">
-        <v>0.56993484271671502</v>
+        <v>0.5697630735988712</v>
       </c>
       <c r="M20">
-        <v>0.54451619918646166</v>
+        <v>0.5422588137568572</v>
       </c>
       <c r="N20">
-        <v>0.51941732173490718</v>
+        <v>0.5207899725358203</v>
       </c>
       <c r="O20">
-        <v>0.51301311626419122</v>
+        <v>0.5157607058078953</v>
       </c>
       <c r="P20">
-        <v>0.48688226460154821</v>
+        <v>0.4928270958398208</v>
       </c>
       <c r="Q20">
-        <v>0.46154251764060389</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>0.4722141956514787</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>0.46211591792587958</v>
+        <v>0.4594094967201821</v>
       </c>
       <c r="D21">
-        <v>0.59472972432286342</v>
+        <v>0.5917621620045774</v>
       </c>
       <c r="E21">
-        <v>0.58244290795904397</v>
+        <v>0.5773449418066126</v>
       </c>
       <c r="F21">
-        <v>0.54189837506674243</v>
+        <v>0.5365997377830849</v>
       </c>
       <c r="G21">
-        <v>0.57473399263896807</v>
+        <v>0.5694354552847616</v>
       </c>
       <c r="H21">
-        <v>0.56888220602867823</v>
+        <v>0.5576961020148301</v>
       </c>
       <c r="I21">
-        <v>0.50762965438060348</v>
+        <v>0.4988121814989039</v>
       </c>
       <c r="J21">
-        <v>0.44573815868920891</v>
+        <v>0.4332271354968424</v>
       </c>
       <c r="K21">
-        <v>0.42524499633752721</v>
+        <v>0.4135817208280108</v>
       </c>
       <c r="L21">
-        <v>0.39066407720763502</v>
+        <v>0.379157856814734</v>
       </c>
       <c r="M21">
-        <v>0.37826370125301018</v>
+        <v>0.3669193569855166</v>
       </c>
       <c r="N21">
-        <v>0.36468629162149491</v>
+        <v>0.3584796034121402</v>
       </c>
       <c r="O21">
-        <v>0.36673108617094419</v>
+        <v>0.358657109321518</v>
       </c>
       <c r="P21">
-        <v>0.37224624040022591</v>
+        <v>0.3662511898578257</v>
       </c>
       <c r="Q21">
-        <v>0.35402625361168011</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>0.3496131153966723</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>0.45910909807390538</v>
+        <v>0.4585224463223009</v>
       </c>
       <c r="D22">
-        <v>0.5931609557927251</v>
+        <v>0.5922650287191309</v>
       </c>
       <c r="E22">
-        <v>0.58306503292145573</v>
+        <v>0.5795517816912952</v>
       </c>
       <c r="F22">
-        <v>0.54210993178928912</v>
+        <v>0.5327466401852715</v>
       </c>
       <c r="G22">
-        <v>0.57282906179320014</v>
+        <v>0.5728129017844955</v>
       </c>
       <c r="H22">
-        <v>0.57558559538832155</v>
+        <v>0.5733642259025805</v>
       </c>
       <c r="I22">
-        <v>0.50838991626694063</v>
+        <v>0.5086481354375327</v>
       </c>
       <c r="J22">
-        <v>0.44801684740476472</v>
+        <v>0.4527241006196184</v>
       </c>
       <c r="K22">
-        <v>0.41532735311570229</v>
+        <v>0.4211246233507139</v>
       </c>
       <c r="L22">
-        <v>0.40126506084881591</v>
+        <v>0.4048716853945379</v>
       </c>
       <c r="M22">
-        <v>0.38027298544608978</v>
+        <v>0.377273312417102</v>
       </c>
       <c r="N22">
-        <v>0.37652040233372153</v>
+        <v>0.3733434522000036</v>
       </c>
       <c r="O22">
-        <v>0.38802333858801158</v>
+        <v>0.3781146936590822</v>
       </c>
       <c r="P22">
-        <v>0.39271956590512852</v>
+        <v>0.3803303859355568</v>
       </c>
       <c r="Q22">
-        <v>0.35603669187811759</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>0.3491629838298661</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>0.59857063444073644</v>
+        <v>0.5986823751912357</v>
       </c>
       <c r="D23">
-        <v>0.59737036929116172</v>
+        <v>0.5967550790986996</v>
       </c>
       <c r="E23">
-        <v>0.57779956864228321</v>
+        <v>0.5767383474364214</v>
       </c>
       <c r="F23">
-        <v>0.59853871963405314</v>
+        <v>0.5993398950115182</v>
       </c>
       <c r="G23">
-        <v>0.54117847410842435</v>
+        <v>0.5407008956124489</v>
       </c>
       <c r="H23">
-        <v>0.49669656026459741</v>
+        <v>0.4877450919148572</v>
       </c>
       <c r="I23">
-        <v>0.42926078771710152</v>
+        <v>0.427686584466544</v>
       </c>
       <c r="J23">
-        <v>0.41155146532415032</v>
+        <v>0.4098257213324562</v>
       </c>
       <c r="K23">
-        <v>0.42086760214329338</v>
+        <v>0.4242356891821279</v>
       </c>
       <c r="L23">
-        <v>0.37980828290537483</v>
+        <v>0.381739865475829</v>
       </c>
       <c r="M23">
-        <v>0.35480160723692949</v>
+        <v>0.3563541371338694</v>
       </c>
       <c r="N23">
-        <v>0.3363616891133186</v>
+        <v>0.3333556180296163</v>
       </c>
       <c r="O23">
-        <v>0.30779795861081538</v>
+        <v>0.3084708376245854</v>
       </c>
       <c r="P23">
-        <v>0.29671222235118311</v>
+        <v>0.2967073881625283</v>
       </c>
       <c r="Q23">
-        <v>0.26878094457865648</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>0.2671532111969103</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>0.1382554658385588</v>
+        <v>0.5934885223214688</v>
       </c>
       <c r="D24">
-        <v>0.17915192293124951</v>
+        <v>0.6258504372193241</v>
       </c>
       <c r="E24">
-        <v>0.2065336884868893</v>
+        <v>0.6017023910180581</v>
       </c>
       <c r="F24">
-        <v>0.17594938887564551</v>
+        <v>0.6209745694250984</v>
       </c>
       <c r="G24">
-        <v>5.794921931254747E-2</v>
+        <v>0.6176128291677047</v>
       </c>
       <c r="H24">
-        <v>7.2375162602698162E-2</v>
+        <v>0.6220736538754028</v>
       </c>
       <c r="I24">
-        <v>7.9702089011233889E-3</v>
+        <v>0.6086577868072386</v>
       </c>
       <c r="J24">
-        <v>-9.6025010179702636E-2</v>
+        <v>0.5867579546165964</v>
       </c>
       <c r="K24">
-        <v>-0.22300105399218309</v>
+        <v>0.5941106729750146</v>
       </c>
       <c r="L24">
-        <v>-0.30779283956946041</v>
+        <v>0.5854319288143235</v>
       </c>
       <c r="M24">
-        <v>-0.31153164613013112</v>
+        <v>0.5626108741672166</v>
       </c>
       <c r="N24">
-        <v>-0.31049949776171482</v>
+        <v>0.5087939235329731</v>
       </c>
       <c r="O24">
-        <v>-0.25510976634328519</v>
+        <v>0.4771745486594925</v>
       </c>
       <c r="P24">
-        <v>-0.22276756725199279</v>
+        <v>0.4144713933144742</v>
       </c>
       <c r="Q24">
-        <v>-0.2264129336324785</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>0.3518792851084365</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>0.1071061921295369</v>
+        <v>0.5972785101075291</v>
       </c>
       <c r="D25">
-        <v>0.13104513516659569</v>
+        <v>0.6293092126345329</v>
       </c>
       <c r="E25">
-        <v>0.13575440869955621</v>
+        <v>0.604351580133934</v>
       </c>
       <c r="F25">
-        <v>0.15321202809935819</v>
+        <v>0.6225059580134844</v>
       </c>
       <c r="G25">
-        <v>0.14136103425941621</v>
+        <v>0.6118472301642182</v>
       </c>
       <c r="H25">
-        <v>3.7836767815972248E-2</v>
+        <v>0.5906463178018146</v>
       </c>
       <c r="I25">
-        <v>-8.3379014104155977E-2</v>
+        <v>0.5617118212276521</v>
       </c>
       <c r="J25">
-        <v>-0.22591961583337439</v>
+        <v>0.5666825876818999</v>
       </c>
       <c r="K25">
-        <v>-0.38203705898521212</v>
+        <v>0.5717386242421354</v>
       </c>
       <c r="L25">
-        <v>-0.50660774267303577</v>
+        <v>0.5817932866474412</v>
       </c>
       <c r="M25">
-        <v>-0.6433355192514939</v>
+        <v>0.5629827626310441</v>
       </c>
       <c r="N25">
-        <v>-0.77612549586765534</v>
+        <v>0.5337867039550176</v>
       </c>
       <c r="O25">
-        <v>-0.84996384693485416</v>
+        <v>0.4891000991504086</v>
       </c>
       <c r="P25">
-        <v>-0.93292954409867945</v>
+        <v>0.4527739929027468</v>
       </c>
       <c r="Q25">
-        <v>-0.97556729914787044</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>0.3861000846123437</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>0.1183952588670345</v>
+        <v>0.6253818160041873</v>
       </c>
       <c r="D26">
-        <v>0.15421444015442681</v>
+        <v>0.6292621450337401</v>
       </c>
       <c r="E26">
-        <v>0.18525679420806049</v>
+        <v>0.6066493380222926</v>
       </c>
       <c r="F26">
-        <v>0.2025042704186861</v>
+        <v>0.6247573198780786</v>
       </c>
       <c r="G26">
-        <v>0.18420383457567061</v>
+        <v>0.6198159138617596</v>
       </c>
       <c r="H26">
-        <v>0.15690236250250689</v>
+        <v>0.624636916538303</v>
       </c>
       <c r="I26">
-        <v>0.1237365430811897</v>
+        <v>0.6078651961448228</v>
       </c>
       <c r="J26">
-        <v>0.1177829598408337</v>
+        <v>0.5877667929361369</v>
       </c>
       <c r="K26">
-        <v>0.121224238483578</v>
+        <v>0.5827428790418099</v>
       </c>
       <c r="L26">
-        <v>0.1150367842969004</v>
+        <v>0.57303436264969</v>
       </c>
       <c r="M26">
-        <v>9.090658271937356E-2</v>
+        <v>0.5337226709850578</v>
       </c>
       <c r="N26">
-        <v>6.1078917287262557E-2</v>
+        <v>0.493737014634747</v>
       </c>
       <c r="O26">
-        <v>-1.40512531861531E-2</v>
+        <v>0.4346803976452118</v>
       </c>
       <c r="P26">
-        <v>-1.979093866069748E-2</v>
+        <v>0.3755868763995021</v>
       </c>
       <c r="Q26">
-        <v>-6.0509227014555932E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>0.2722154700109565</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>9.032641339285305E-2</v>
+        <v>0.6253737102441186</v>
       </c>
       <c r="D27">
-        <v>0.123644724313102</v>
+        <v>0.6286354264906843</v>
       </c>
       <c r="E27">
-        <v>0.17951268746540841</v>
+        <v>0.6073370634487254</v>
       </c>
       <c r="F27">
-        <v>0.22521188643653189</v>
+        <v>0.6243918463438123</v>
       </c>
       <c r="G27">
-        <v>0.1920295845111086</v>
+        <v>0.6220316335922121</v>
       </c>
       <c r="H27">
-        <v>0.12524887881017119</v>
+        <v>0.6259372920788489</v>
       </c>
       <c r="I27">
-        <v>0.1001706954284209</v>
+        <v>0.6203358226392128</v>
       </c>
       <c r="J27">
-        <v>7.855488531364295E-2</v>
+        <v>0.613606105003614</v>
       </c>
       <c r="K27">
-        <v>6.3634167752307541E-2</v>
+        <v>0.6214616222961766</v>
       </c>
       <c r="L27">
-        <v>5.4895156565319833E-2</v>
+        <v>0.6286702279020031</v>
       </c>
       <c r="M27">
-        <v>3.2024439732663203E-2</v>
+        <v>0.6244246597706591</v>
       </c>
       <c r="N27">
-        <v>-3.1124878256998442E-2</v>
+        <v>0.6084071825857746</v>
       </c>
       <c r="O27">
-        <v>-8.0753118840822632E-2</v>
+        <v>0.5766175356602479</v>
       </c>
       <c r="P27">
-        <v>-0.17131624654979069</v>
+        <v>0.5692240128230974</v>
       </c>
       <c r="Q27">
-        <v>-0.25547553394923839</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>0.4931352187780187</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.59419350090933742</v>
+        <v>0.5979660677624783</v>
       </c>
       <c r="D28">
-        <v>0.6265482244614089</v>
+        <v>0.6298139121999458</v>
       </c>
       <c r="E28">
-        <v>0.6030351253473516</v>
+        <v>0.6035210142959742</v>
       </c>
       <c r="F28">
-        <v>0.62137421883587152</v>
+        <v>0.6223056877541866</v>
       </c>
       <c r="G28">
-        <v>0.61855192067880671</v>
+        <v>0.6109722231908266</v>
       </c>
       <c r="H28">
-        <v>0.62395062509966481</v>
+        <v>0.5942075462530816</v>
       </c>
       <c r="I28">
-        <v>0.60578451293890268</v>
+        <v>0.574245173534681</v>
       </c>
       <c r="J28">
-        <v>0.58671656712206632</v>
+        <v>0.5893812613166354</v>
       </c>
       <c r="K28">
-        <v>0.59460659954284623</v>
+        <v>0.5917405174755618</v>
       </c>
       <c r="L28">
-        <v>0.5869640463977065</v>
+        <v>0.6087455655997113</v>
       </c>
       <c r="M28">
-        <v>0.5659660640913482</v>
+        <v>0.6038632603998236</v>
       </c>
       <c r="N28">
-        <v>0.51727552250408237</v>
+        <v>0.5899063124772749</v>
       </c>
       <c r="O28">
-        <v>0.48391503666187391</v>
+        <v>0.5591888322778202</v>
       </c>
       <c r="P28">
-        <v>0.42544977336745082</v>
+        <v>0.552172389567211</v>
       </c>
       <c r="Q28">
-        <v>0.36740037801607228</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>0.5135090394615178</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.5987249016142806</v>
+        <v>0.5967554722830209</v>
       </c>
       <c r="D29">
-        <v>0.63040204588104687</v>
+        <v>0.6292448430559687</v>
       </c>
       <c r="E29">
-        <v>0.60539676329811254</v>
+        <v>0.6035937861420456</v>
       </c>
       <c r="F29">
-        <v>0.62437746584595188</v>
+        <v>0.6208259147787204</v>
       </c>
       <c r="G29">
-        <v>0.61280549487958669</v>
+        <v>0.6108141879716894</v>
       </c>
       <c r="H29">
-        <v>0.59088448325046883</v>
+        <v>0.5949856691770429</v>
       </c>
       <c r="I29">
-        <v>0.55983595202222225</v>
+        <v>0.5761287914708833</v>
       </c>
       <c r="J29">
-        <v>0.57235108916963928</v>
+        <v>0.5871704458927809</v>
       </c>
       <c r="K29">
-        <v>0.56412832188391704</v>
+        <v>0.5883575966688835</v>
       </c>
       <c r="L29">
-        <v>0.57758373067756497</v>
+        <v>0.6055704404911495</v>
       </c>
       <c r="M29">
-        <v>0.5530391988030845</v>
+        <v>0.6034246289846346</v>
       </c>
       <c r="N29">
-        <v>0.52128633663327228</v>
+        <v>0.5951937542239877</v>
       </c>
       <c r="O29">
-        <v>0.47260839323936221</v>
+        <v>0.5679469680102267</v>
       </c>
       <c r="P29">
-        <v>0.43247322148881268</v>
+        <v>0.5657044679676012</v>
       </c>
       <c r="Q29">
-        <v>0.36607292292087901</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>0.5276548358348159</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.62521784081969123</v>
+        <v>0.597190857656735</v>
       </c>
       <c r="D30">
-        <v>0.62987543469901419</v>
+        <v>0.6295655152078538</v>
       </c>
       <c r="E30">
-        <v>0.61061751512657758</v>
+        <v>0.6056640477958737</v>
       </c>
       <c r="F30">
-        <v>0.62645610071401425</v>
+        <v>0.6255503326917495</v>
       </c>
       <c r="G30">
-        <v>0.62332134601907996</v>
+        <v>0.6156284140288003</v>
       </c>
       <c r="H30">
-        <v>0.62469855439097621</v>
+        <v>0.6013513047779631</v>
       </c>
       <c r="I30">
-        <v>0.60989916518100662</v>
+        <v>0.5852136116242659</v>
       </c>
       <c r="J30">
-        <v>0.58586856750671734</v>
+        <v>0.6005242296045683</v>
       </c>
       <c r="K30">
-        <v>0.58442144823377284</v>
+        <v>0.6021066238035712</v>
       </c>
       <c r="L30">
-        <v>0.57594333681185639</v>
+        <v>0.6136754060745586</v>
       </c>
       <c r="M30">
-        <v>0.54173354546552965</v>
+        <v>0.6130932689383987</v>
       </c>
       <c r="N30">
-        <v>0.49998256512123251</v>
+        <v>0.607695152902066</v>
       </c>
       <c r="O30">
-        <v>0.44207455432032772</v>
+        <v>0.5830104642593321</v>
       </c>
       <c r="P30">
-        <v>0.38688863936112011</v>
+        <v>0.5795103693884839</v>
       </c>
       <c r="Q30">
-        <v>0.28582526436175121</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>0.5459966392545235</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.62583181307683577</v>
+        <v>0.5983343541481473</v>
       </c>
       <c r="D31">
-        <v>0.63015441774435543</v>
+        <v>0.6309010242390727</v>
       </c>
       <c r="E31">
-        <v>0.61064828754187694</v>
+        <v>0.6068894101078016</v>
       </c>
       <c r="F31">
-        <v>0.6262531529026506</v>
+        <v>0.6233681569294257</v>
       </c>
       <c r="G31">
-        <v>0.62237927829247452</v>
+        <v>0.6146517710490463</v>
       </c>
       <c r="H31">
-        <v>0.62807294037467842</v>
+        <v>0.5991730024421331</v>
       </c>
       <c r="I31">
-        <v>0.62282788127359823</v>
+        <v>0.5843160841940586</v>
       </c>
       <c r="J31">
-        <v>0.6160662269467897</v>
+        <v>0.5938111638149998</v>
       </c>
       <c r="K31">
-        <v>0.62135345497646344</v>
+        <v>0.5921686726585854</v>
       </c>
       <c r="L31">
-        <v>0.63207382781649835</v>
+        <v>0.6111347055481133</v>
       </c>
       <c r="M31">
-        <v>0.62816169752379925</v>
+        <v>0.6100952273588983</v>
       </c>
       <c r="N31">
-        <v>0.61046955760493249</v>
+        <v>0.6060348789017382</v>
       </c>
       <c r="O31">
-        <v>0.57703601877648691</v>
+        <v>0.5850981910248567</v>
       </c>
       <c r="P31">
-        <v>0.57385161032075516</v>
+        <v>0.5791066047757251</v>
       </c>
       <c r="Q31">
-        <v>0.49887931566800708</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>0.5603870836899643</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.59737521730402976</v>
+        <v>0.5981123547563237</v>
       </c>
       <c r="D32">
-        <v>0.62910880162603855</v>
+        <v>0.6291055290759393</v>
       </c>
       <c r="E32">
-        <v>0.60308839749857179</v>
+        <v>0.6009622113891995</v>
       </c>
       <c r="F32">
-        <v>0.62264414100801946</v>
+        <v>0.6212864783545687</v>
       </c>
       <c r="G32">
-        <v>0.61336004895078311</v>
+        <v>0.6103563291087259</v>
       </c>
       <c r="H32">
-        <v>0.59871826588189614</v>
+        <v>0.5907734513579633</v>
       </c>
       <c r="I32">
-        <v>0.57890932453255051</v>
+        <v>0.5727002799236942</v>
       </c>
       <c r="J32">
-        <v>0.59560173816163697</v>
+        <v>0.5804865279366238</v>
       </c>
       <c r="K32">
-        <v>0.59747941058644827</v>
+        <v>0.5863231234250736</v>
       </c>
       <c r="L32">
-        <v>0.60983952325054314</v>
+        <v>0.6061586030865854</v>
       </c>
       <c r="M32">
-        <v>0.60519157354360364</v>
+        <v>0.6018881855054367</v>
       </c>
       <c r="N32">
-        <v>0.59581821439618832</v>
+        <v>0.5838908835157637</v>
       </c>
       <c r="O32">
-        <v>0.56535404976155557</v>
+        <v>0.5547389273358089</v>
       </c>
       <c r="P32">
-        <v>0.55479846640496489</v>
+        <v>0.5577710207640508</v>
       </c>
       <c r="Q32">
-        <v>0.51854441218532521</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>0.5294600159933327</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.59674339421793376</v>
+        <v>0.5982819530010279</v>
       </c>
       <c r="D33">
-        <v>0.63008871256249954</v>
+        <v>0.6299211515938394</v>
       </c>
       <c r="E33">
-        <v>0.60520964633574115</v>
+        <v>0.6059829623311739</v>
       </c>
       <c r="F33">
-        <v>0.62197572909548104</v>
+        <v>0.62316706090326</v>
       </c>
       <c r="G33">
-        <v>0.61222660149129549</v>
+        <v>0.6128184524604449</v>
       </c>
       <c r="H33">
-        <v>0.59504321410907679</v>
+        <v>0.5935250159643283</v>
       </c>
       <c r="I33">
-        <v>0.57798479355324528</v>
+        <v>0.5730318453597777</v>
       </c>
       <c r="J33">
-        <v>0.5878920991299369</v>
+        <v>0.5851666795119749</v>
       </c>
       <c r="K33">
-        <v>0.58946693660861671</v>
+        <v>0.5924257710150699</v>
       </c>
       <c r="L33">
-        <v>0.60885279990845809</v>
+        <v>0.6116110271146136</v>
       </c>
       <c r="M33">
-        <v>0.60850839286236003</v>
+        <v>0.6105209588876502</v>
       </c>
       <c r="N33">
-        <v>0.59961329009376341</v>
+        <v>0.5959755711617106</v>
       </c>
       <c r="O33">
-        <v>0.57175532608750756</v>
+        <v>0.5685048840214203</v>
       </c>
       <c r="P33">
-        <v>0.56688241442003329</v>
+        <v>0.5681073974235353</v>
       </c>
       <c r="Q33">
-        <v>0.53236027795051899</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>0.5432852410470904</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.59600117203513614</v>
+        <v>0.5965466009276867</v>
       </c>
       <c r="D34">
-        <v>0.62762369621550695</v>
+        <v>0.6287520800128935</v>
       </c>
       <c r="E34">
-        <v>0.60112067779781575</v>
+        <v>0.6022126057586739</v>
       </c>
       <c r="F34">
-        <v>0.61709235639310234</v>
+        <v>0.6209156080989726</v>
       </c>
       <c r="G34">
-        <v>0.60790237025409266</v>
+        <v>0.6107307603157536</v>
       </c>
       <c r="H34">
-        <v>0.59191969313428772</v>
+        <v>0.5962983241614153</v>
       </c>
       <c r="I34">
-        <v>0.5747819181927849</v>
+        <v>0.5772241078608343</v>
       </c>
       <c r="J34">
-        <v>0.58728350134622942</v>
+        <v>0.5892348795007754</v>
       </c>
       <c r="K34">
-        <v>0.59208948636332037</v>
+        <v>0.5933550789970321</v>
       </c>
       <c r="L34">
-        <v>0.60687022026385118</v>
+        <v>0.6143521292366032</v>
       </c>
       <c r="M34">
-        <v>0.60772730584018031</v>
+        <v>0.6091929992294639</v>
       </c>
       <c r="N34">
-        <v>0.59831364366659257</v>
+        <v>0.5945637108168182</v>
       </c>
       <c r="O34">
-        <v>0.57591647813444324</v>
+        <v>0.5696233327867892</v>
       </c>
       <c r="P34">
-        <v>0.57179137959819759</v>
+        <v>0.5741952625943242</v>
       </c>
       <c r="Q34">
-        <v>0.54219091022893873</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>0.5462957336010502</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.59677644979927247</v>
+        <v>0.5983205485742765</v>
       </c>
       <c r="D35">
-        <v>0.6297947033509449</v>
+        <v>0.6308585888014309</v>
       </c>
       <c r="E35">
-        <v>0.6055582216908052</v>
+        <v>0.607097806784521</v>
       </c>
       <c r="F35">
-        <v>0.62248470354923802</v>
+        <v>0.6230476406661273</v>
       </c>
       <c r="G35">
-        <v>0.61194540219684956</v>
+        <v>0.6147740012290861</v>
       </c>
       <c r="H35">
-        <v>0.59345452927551379</v>
+        <v>0.598632636116593</v>
       </c>
       <c r="I35">
-        <v>0.57713644998258107</v>
+        <v>0.5839370089065129</v>
       </c>
       <c r="J35">
-        <v>0.58948132920571683</v>
+        <v>0.5938867622313976</v>
       </c>
       <c r="K35">
-        <v>0.58925287137094839</v>
+        <v>0.5927354767318285</v>
       </c>
       <c r="L35">
-        <v>0.60736385596547449</v>
+        <v>0.6118052554052151</v>
       </c>
       <c r="M35">
-        <v>0.60602381329562105</v>
+        <v>0.610907119226102</v>
       </c>
       <c r="N35">
-        <v>0.60393918599691576</v>
+        <v>0.600493287904543</v>
       </c>
       <c r="O35">
-        <v>0.58376226484504834</v>
+        <v>0.5755411555177274</v>
       </c>
       <c r="P35">
-        <v>0.58017531390969457</v>
+        <v>0.5784789277507388</v>
       </c>
       <c r="Q35">
-        <v>0.55853582772513399</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>0.5553502059021389</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.59726682577077328</v>
+        <v>0.5973986270969242</v>
       </c>
       <c r="D36">
-        <v>0.62956780580029181</v>
+        <v>0.6302191615886715</v>
       </c>
       <c r="E36">
-        <v>0.60584747054161292</v>
+        <v>0.6047729413450942</v>
       </c>
       <c r="F36">
-        <v>0.62365099272206581</v>
+        <v>0.6219527045366355</v>
       </c>
       <c r="G36">
-        <v>0.61385813542240553</v>
+        <v>0.6131057187118798</v>
       </c>
       <c r="H36">
-        <v>0.59960783829176845</v>
+        <v>0.5971983464715483</v>
       </c>
       <c r="I36">
-        <v>0.57962197998473253</v>
+        <v>0.5781335197242551</v>
       </c>
       <c r="J36">
-        <v>0.590443479560953</v>
+        <v>0.5901379194476916</v>
       </c>
       <c r="K36">
-        <v>0.5888360596709189</v>
+        <v>0.592303227498431</v>
       </c>
       <c r="L36">
-        <v>0.61043058907584891</v>
+        <v>0.6097338329288984</v>
       </c>
       <c r="M36">
-        <v>0.60677722385555322</v>
+        <v>0.6073023305435077</v>
       </c>
       <c r="N36">
-        <v>0.59124056835719963</v>
+        <v>0.605429360631802</v>
       </c>
       <c r="O36">
-        <v>0.56176415040494765</v>
+        <v>0.5818376264613488</v>
       </c>
       <c r="P36">
-        <v>0.56572146126479816</v>
+        <v>0.5801445912106643</v>
       </c>
       <c r="Q36">
-        <v>0.53527935683246464</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>0.5644621179764001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>0.5978821017815672</v>
+        <v>0.6319831478123158</v>
       </c>
       <c r="D37">
-        <v>0.6299326621702015</v>
+        <v>0.6298334709520158</v>
       </c>
       <c r="E37">
-        <v>0.60590315711243314</v>
+        <v>0.6293310574607023</v>
       </c>
       <c r="F37">
-        <v>0.62338528542447913</v>
+        <v>0.6281425149536812</v>
       </c>
       <c r="G37">
-        <v>0.61414417628848106</v>
+        <v>0.5976180638805242</v>
       </c>
       <c r="H37">
-        <v>0.59836293049694256</v>
+        <v>0.5696571615683536</v>
       </c>
       <c r="I37">
-        <v>0.57979443172819667</v>
+        <v>0.5861980571914297</v>
       </c>
       <c r="J37">
-        <v>0.59324524896458508</v>
+        <v>0.5751892001982707</v>
       </c>
       <c r="K37">
-        <v>0.59516680290880464</v>
+        <v>0.5625180062419399</v>
       </c>
       <c r="L37">
-        <v>0.61478254720714764</v>
+        <v>0.5272172628910261</v>
       </c>
       <c r="M37">
-        <v>0.60822666159500338</v>
+        <v>0.4815660284953596</v>
       </c>
       <c r="N37">
-        <v>0.59877059474770222</v>
+        <v>0.4223315551744488</v>
       </c>
       <c r="O37">
-        <v>0.5739534259971083</v>
+        <v>0.3345535787313146</v>
       </c>
       <c r="P37">
-        <v>0.5758480402949786</v>
+        <v>0.2778819866403686</v>
       </c>
       <c r="Q37">
-        <v>0.55323107391025839</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>0.2228010330702021</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>0.59778379949565807</v>
+        <v>0.6283314248539937</v>
       </c>
       <c r="D38">
-        <v>0.63002419279566801</v>
+        <v>0.6295143037516912</v>
       </c>
       <c r="E38">
-        <v>0.60685419974695398</v>
+        <v>0.6321178416584672</v>
       </c>
       <c r="F38">
-        <v>0.62311645092239809</v>
+        <v>0.6325210862943751</v>
       </c>
       <c r="G38">
-        <v>0.61267377675427925</v>
+        <v>0.6177942424464151</v>
       </c>
       <c r="H38">
-        <v>0.59546987257837047</v>
+        <v>0.6010430435740617</v>
       </c>
       <c r="I38">
-        <v>0.5772423943014261</v>
+        <v>0.599325372080844</v>
       </c>
       <c r="J38">
-        <v>0.59138182004798967</v>
+        <v>0.5714472422559815</v>
       </c>
       <c r="K38">
-        <v>0.59620786457297548</v>
+        <v>0.5102644164450149</v>
       </c>
       <c r="L38">
-        <v>0.61720337884045873</v>
+        <v>0.482411851869546</v>
       </c>
       <c r="M38">
-        <v>0.61525506693857868</v>
+        <v>0.4698564720756657</v>
       </c>
       <c r="N38">
-        <v>0.60339358642229779</v>
+        <v>0.4908699552215187</v>
       </c>
       <c r="O38">
-        <v>0.57696410669805309</v>
+        <v>0.5086184798112612</v>
       </c>
       <c r="P38">
-        <v>0.5826177800160165</v>
+        <v>0.4892998881320823</v>
       </c>
       <c r="Q38">
-        <v>0.5586109038089675</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>0.4679414453226308</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>0.59709787952568993</v>
+        <v>0.628816545312174</v>
       </c>
       <c r="D39">
-        <v>0.62917409650851586</v>
+        <v>0.6284350182280195</v>
       </c>
       <c r="E39">
-        <v>0.6036321218976719</v>
+        <v>0.6326256329068237</v>
       </c>
       <c r="F39">
-        <v>0.62173835974805058</v>
+        <v>0.6316155965162789</v>
       </c>
       <c r="G39">
-        <v>0.61220237275232725</v>
+        <v>0.6173431115136748</v>
       </c>
       <c r="H39">
-        <v>0.59555913194032573</v>
+        <v>0.6031438663670634</v>
       </c>
       <c r="I39">
-        <v>0.57534411571208255</v>
+        <v>0.615075419879871</v>
       </c>
       <c r="J39">
-        <v>0.58521895881151376</v>
+        <v>0.5974202708609596</v>
       </c>
       <c r="K39">
-        <v>0.58891654717005082</v>
+        <v>0.5245460585794742</v>
       </c>
       <c r="L39">
-        <v>0.61173803309595898</v>
+        <v>0.5022953174739677</v>
       </c>
       <c r="M39">
-        <v>0.60875777031551459</v>
+        <v>0.4887054060607111</v>
       </c>
       <c r="N39">
-        <v>0.59145348729508362</v>
+        <v>0.4817065181585592</v>
       </c>
       <c r="O39">
-        <v>0.56866419577082206</v>
+        <v>0.4830602051810329</v>
       </c>
       <c r="P39">
-        <v>0.57120000281111172</v>
+        <v>0.4819289188066779</v>
       </c>
       <c r="Q39">
-        <v>0.54995024105853918</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>0.4437121109955692</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>0.5984604500625712</v>
+        <v>0.5935608743064132</v>
       </c>
       <c r="D40">
-        <v>0.62954788851915855</v>
+        <v>0.5857924748211119</v>
       </c>
       <c r="E40">
-        <v>0.6006298891881573</v>
+        <v>0.5697095367490579</v>
       </c>
       <c r="F40">
-        <v>0.61928503950180236</v>
+        <v>0.6031674254669076</v>
       </c>
       <c r="G40">
-        <v>0.61028012092590644</v>
+        <v>0.6210334881073715</v>
       </c>
       <c r="H40">
-        <v>0.59524944770544219</v>
+        <v>0.5927822152376228</v>
       </c>
       <c r="I40">
-        <v>0.57852399427383516</v>
+        <v>0.5553813160123359</v>
       </c>
       <c r="J40">
-        <v>0.59183880316182058</v>
+        <v>0.5221998150127227</v>
       </c>
       <c r="K40">
-        <v>0.58951069568926751</v>
+        <v>0.5034864855964408</v>
       </c>
       <c r="L40">
-        <v>0.60778505597732613</v>
+        <v>0.4818498928032821</v>
       </c>
       <c r="M40">
-        <v>0.60760606762050373</v>
+        <v>0.439959500999161</v>
       </c>
       <c r="N40">
-        <v>0.60281332444896185</v>
+        <v>0.3577729313257353</v>
       </c>
       <c r="O40">
-        <v>0.58384178659469332</v>
+        <v>0.255366874017857</v>
       </c>
       <c r="P40">
-        <v>0.581663817291453</v>
+        <v>0.1567117136470396</v>
       </c>
       <c r="Q40">
-        <v>0.56715342854466821</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>0.1060963969453542</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>0.63095909201145284</v>
+        <v>0.5857595008498613</v>
       </c>
       <c r="D41">
-        <v>0.6311601953878897</v>
+        <v>0.6113013615069568</v>
       </c>
       <c r="E41">
-        <v>0.63097026773356113</v>
+        <v>0.5530348672991638</v>
       </c>
       <c r="F41">
-        <v>0.62813867866075845</v>
+        <v>0.5453535789350331</v>
       </c>
       <c r="G41">
-        <v>0.5980925580391544</v>
+        <v>0.5570333365996577</v>
       </c>
       <c r="H41">
-        <v>0.56811365763677268</v>
+        <v>0.5082074662141096</v>
       </c>
       <c r="I41">
-        <v>0.58516785291284645</v>
+        <v>0.4966989580261165</v>
       </c>
       <c r="J41">
-        <v>0.57283727650214855</v>
+        <v>0.4902622556603111</v>
       </c>
       <c r="K41">
-        <v>0.55620731672494794</v>
+        <v>0.463540778257415</v>
       </c>
       <c r="L41">
-        <v>0.52388855216146091</v>
+        <v>0.430264654306641</v>
       </c>
       <c r="M41">
-        <v>0.4804673709513026</v>
+        <v>0.3765677302659472</v>
       </c>
       <c r="N41">
-        <v>0.42106467971846728</v>
+        <v>0.2818984390508165</v>
       </c>
       <c r="O41">
-        <v>0.33064521089054061</v>
+        <v>0.2436968373199161</v>
       </c>
       <c r="P41">
-        <v>0.27420910205874671</v>
+        <v>0.2038701690763918</v>
       </c>
       <c r="Q41">
-        <v>0.21685849769647761</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>0.1767702997632739</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>0.62941068213827422</v>
+        <v>0.4617035365669464</v>
       </c>
       <c r="D42">
-        <v>0.63093798746665308</v>
+        <v>0.610181922835112</v>
       </c>
       <c r="E42">
-        <v>0.63008378112164942</v>
+        <v>0.5724653041328985</v>
       </c>
       <c r="F42">
-        <v>0.63142098083200648</v>
+        <v>0.5210364606148404</v>
       </c>
       <c r="G42">
-        <v>0.61756136973862841</v>
+        <v>0.5436869667195766</v>
       </c>
       <c r="H42">
-        <v>0.60260298959499514</v>
+        <v>0.5600078884905455</v>
       </c>
       <c r="I42">
-        <v>0.60117350290805749</v>
+        <v>0.5405200881409535</v>
       </c>
       <c r="J42">
-        <v>0.56939639788795049</v>
+        <v>0.4778467604889289</v>
       </c>
       <c r="K42">
-        <v>0.5065684713916675</v>
+        <v>0.4092466087643933</v>
       </c>
       <c r="L42">
-        <v>0.47771696970755267</v>
+        <v>0.3623469649915194</v>
       </c>
       <c r="M42">
-        <v>0.46619744987379319</v>
+        <v>0.3221431356929617</v>
       </c>
       <c r="N42">
-        <v>0.48928779215128021</v>
+        <v>0.2964890701855939</v>
       </c>
       <c r="O42">
-        <v>0.50611169074027407</v>
+        <v>0.2711089765873933</v>
       </c>
       <c r="P42">
-        <v>0.48435579528328421</v>
+        <v>0.2259799655467406</v>
       </c>
       <c r="Q42">
-        <v>0.46403039656409178</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>0.1760857710788321</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>0.63076489532468683</v>
+        <v>0.612532829099214</v>
       </c>
       <c r="D43">
-        <v>0.63310979185946059</v>
+        <v>0.5976855507179578</v>
       </c>
       <c r="E43">
-        <v>0.63403675403265247</v>
+        <v>0.5838310903579925</v>
       </c>
       <c r="F43">
-        <v>0.63335273740174092</v>
+        <v>0.5917854990805922</v>
       </c>
       <c r="G43">
-        <v>0.61943386853509641</v>
+        <v>0.5499871159851841</v>
       </c>
       <c r="H43">
-        <v>0.6067097752552727</v>
+        <v>0.546323083656601</v>
       </c>
       <c r="I43">
-        <v>0.61831454348262649</v>
+        <v>0.5200912033896373</v>
       </c>
       <c r="J43">
-        <v>0.60011529042023126</v>
+        <v>0.4995073213625885</v>
       </c>
       <c r="K43">
-        <v>0.52974364047080758</v>
+        <v>0.4582997340494743</v>
       </c>
       <c r="L43">
-        <v>0.50914770188689684</v>
+        <v>0.3990492084740457</v>
       </c>
       <c r="M43">
-        <v>0.49280573907311459</v>
+        <v>0.3391063539165919</v>
       </c>
       <c r="N43">
-        <v>0.48975702817544492</v>
+        <v>0.2891660743689997</v>
       </c>
       <c r="O43">
-        <v>0.49340297154105378</v>
+        <v>0.2705505521415412</v>
       </c>
       <c r="P43">
-        <v>0.4927579003923071</v>
+        <v>0.2667886983454261</v>
       </c>
       <c r="Q43">
-        <v>0.451057939842056</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C44">
-        <v>0.59325899855069353</v>
-      </c>
-      <c r="D44">
-        <v>0.58849412289829073</v>
-      </c>
-      <c r="E44">
-        <v>0.57414392504152001</v>
-      </c>
-      <c r="F44">
-        <v>0.60827573219967945</v>
-      </c>
-      <c r="G44">
-        <v>0.62254126762475248</v>
-      </c>
-      <c r="H44">
-        <v>0.59897179646086574</v>
-      </c>
-      <c r="I44">
-        <v>0.56501274076548702</v>
-      </c>
-      <c r="J44">
-        <v>0.53116894971497552</v>
-      </c>
-      <c r="K44">
-        <v>0.51132636348400184</v>
-      </c>
-      <c r="L44">
-        <v>0.48930347965973903</v>
-      </c>
-      <c r="M44">
-        <v>0.44700085027497261</v>
-      </c>
-      <c r="N44">
-        <v>0.37205348209109879</v>
-      </c>
-      <c r="O44">
-        <v>0.27256788435465962</v>
-      </c>
-      <c r="P44">
-        <v>0.1819863913083494</v>
-      </c>
-      <c r="Q44">
-        <v>0.13345827977673269</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C45">
-        <v>0.58468366840865194</v>
-      </c>
-      <c r="D45">
-        <v>0.60874211222325258</v>
-      </c>
-      <c r="E45">
-        <v>0.54974116117137939</v>
-      </c>
-      <c r="F45">
-        <v>0.542817136041433</v>
-      </c>
-      <c r="G45">
-        <v>0.55615817327951922</v>
-      </c>
-      <c r="H45">
-        <v>0.51457762689789732</v>
-      </c>
-      <c r="I45">
-        <v>0.50198239154211344</v>
-      </c>
-      <c r="J45">
-        <v>0.48943624740074992</v>
-      </c>
-      <c r="K45">
-        <v>0.46216412794067008</v>
-      </c>
-      <c r="L45">
-        <v>0.43267348668222838</v>
-      </c>
-      <c r="M45">
-        <v>0.37852505656101298</v>
-      </c>
-      <c r="N45">
-        <v>0.28717935465056033</v>
-      </c>
-      <c r="O45">
-        <v>0.24965319538173289</v>
-      </c>
-      <c r="P45">
-        <v>0.20725217770185311</v>
-      </c>
-      <c r="Q45">
-        <v>0.1771522340315578</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B46">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C46">
-        <v>0.46265314815284631</v>
-      </c>
-      <c r="D46">
-        <v>0.6092480042851921</v>
-      </c>
-      <c r="E46">
-        <v>0.57071591275812572</v>
-      </c>
-      <c r="F46">
-        <v>0.51732414397676418</v>
-      </c>
-      <c r="G46">
-        <v>0.53657585498332905</v>
-      </c>
-      <c r="H46">
-        <v>0.5579864375732424</v>
-      </c>
-      <c r="I46">
-        <v>0.53969142646589352</v>
-      </c>
-      <c r="J46">
-        <v>0.47404415321461879</v>
-      </c>
-      <c r="K46">
-        <v>0.40791116391446658</v>
-      </c>
-      <c r="L46">
-        <v>0.36035476712637893</v>
-      </c>
-      <c r="M46">
-        <v>0.31394791955197848</v>
-      </c>
-      <c r="N46">
-        <v>0.2916754266913007</v>
-      </c>
-      <c r="O46">
-        <v>0.26688077092210449</v>
-      </c>
-      <c r="P46">
-        <v>0.21931373216701419</v>
-      </c>
-      <c r="Q46">
-        <v>0.17162075574256919</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C47">
-        <v>0.6122877017098638</v>
-      </c>
-      <c r="D47">
-        <v>0.59707692788207178</v>
-      </c>
-      <c r="E47">
-        <v>0.58420854393597055</v>
-      </c>
-      <c r="F47">
-        <v>0.59317317636165734</v>
-      </c>
-      <c r="G47">
-        <v>0.55361858960226629</v>
-      </c>
-      <c r="H47">
-        <v>0.54827386430168734</v>
-      </c>
-      <c r="I47">
-        <v>0.52567979787140906</v>
-      </c>
-      <c r="J47">
-        <v>0.50328705139206964</v>
-      </c>
-      <c r="K47">
-        <v>0.4653837029337668</v>
-      </c>
-      <c r="L47">
-        <v>0.4080542010766357</v>
-      </c>
-      <c r="M47">
-        <v>0.34406990088173423</v>
-      </c>
-      <c r="N47">
-        <v>0.29883210237581231</v>
-      </c>
-      <c r="O47">
-        <v>0.28040995667370971</v>
-      </c>
-      <c r="P47">
-        <v>0.27698846487236478</v>
-      </c>
-      <c r="Q47">
-        <v>0.25814640029049712</v>
+        <v>0.2501311960359755</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:Q47">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>